--- a/s60_signal/position-1398-1288-800.xlsx
+++ b/s60_signal/position-1398-1288-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="614">
   <si>
     <t>trade_time</t>
   </si>
@@ -823,10 +823,10 @@
     <t>2021-06-28</t>
   </si>
   <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2011-05-05</t>
@@ -1853,6 +1853,9 @@
   </si>
   <si>
     <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P845"/>
+  <dimension ref="A1:P848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -41877,10 +41880,10 @@
         <v>1</v>
       </c>
       <c r="B806" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C806">
-        <v>-0.2111041693342441</v>
+        <v>-0.1811041693342443</v>
       </c>
       <c r="D806" t="s">
         <v>267</v>
@@ -41892,13 +41895,13 @@
         <v>1</v>
       </c>
       <c r="G806">
-        <v>0.005611104169334245</v>
+        <v>0.005641104169334245</v>
       </c>
       <c r="H806">
         <v>0.005357463410025915</v>
       </c>
       <c r="I806">
-        <v>0.2536407593083299</v>
+        <v>0.2236407593083301</v>
       </c>
       <c r="J806">
         <v>0.576456271155296</v>
@@ -41907,7 +41910,7 @@
         <v>5.05</v>
       </c>
       <c r="L806">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="M806">
         <v>4.61</v>
@@ -42533,10 +42536,10 @@
         <v>-0.4054252239686154</v>
       </c>
       <c r="D819" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E819">
-        <v>-0.1740483763193672</v>
+        <v>-0.1348535212862014</v>
       </c>
       <c r="F819">
         <v>1</v>
@@ -42545,10 +42548,10 @@
         <v>0.005805425223968616</v>
       </c>
       <c r="H819">
-        <v>0.005594048376319368</v>
+        <v>0.005534853521286202</v>
       </c>
       <c r="I819">
-        <v>0.2313768476492482</v>
+        <v>0.2705717026824139</v>
       </c>
       <c r="J819">
         <v>0.6149356879145773</v>
@@ -42560,10 +42563,10 @@
         <v>2.7</v>
       </c>
       <c r="M819">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N819">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O819">
         <v>1</v>
@@ -42833,10 +42836,10 @@
         <v>-0.4075206413464314</v>
       </c>
       <c r="D825" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E825">
-        <v>-0.1759944174088637</v>
+        <v>-0.1367663676449604</v>
       </c>
       <c r="F825">
         <v>1</v>
@@ -42845,10 +42848,10 @@
         <v>0.005807520641346433</v>
       </c>
       <c r="H825">
-        <v>0.005595994417408864</v>
+        <v>0.005536766367644961</v>
       </c>
       <c r="I825">
-        <v>0.2315262239375677</v>
+        <v>0.270754273701471</v>
       </c>
       <c r="J825">
         <v>0.6153506220487983</v>
@@ -42860,10 +42863,10 @@
         <v>2.7</v>
       </c>
       <c r="M825">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N825">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O825">
         <v>1</v>
@@ -43224,52 +43227,52 @@
     </row>
     <row r="833" spans="1:16">
       <c r="A833" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B833" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C833">
-        <v>0.04151836842568901</v>
+        <v>-0.4367748410424306</v>
       </c>
       <c r="D833" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E833">
-        <v>-0.3071325213637568</v>
+        <v>-0.2031631692057423</v>
       </c>
       <c r="F833">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G833">
-        <v>0.006258481631574311</v>
+        <v>0.00583677484104243</v>
       </c>
       <c r="H833">
-        <v>0.005947132521363757</v>
+        <v>0.005623163169205743</v>
       </c>
       <c r="I833">
-        <v>0.3486508897894458</v>
+        <v>0.2336116718366883</v>
       </c>
       <c r="J833">
-        <v>0.6216963263148622</v>
+        <v>0.6211435328796893</v>
       </c>
       <c r="K833">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="L833">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="M833">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="N833">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="O833">
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43280,28 +43283,28 @@
         <v>108</v>
       </c>
       <c r="C834">
-        <v>0.03761276525581048</v>
+        <v>0.04151836842568901</v>
       </c>
       <c r="D834" t="s">
         <v>265</v>
       </c>
       <c r="E834">
-        <v>-0.3110615581526548</v>
+        <v>-0.3071325213637568</v>
       </c>
       <c r="F834">
         <v>-1</v>
       </c>
       <c r="G834">
-        <v>0.006262387234744189</v>
+        <v>0.006258481631574311</v>
       </c>
       <c r="H834">
-        <v>0.005951061558152654</v>
+        <v>0.005947132521363757</v>
       </c>
       <c r="I834">
-        <v>0.3486743234084653</v>
+        <v>0.3486508897894458</v>
       </c>
       <c r="J834">
-        <v>0.6224774469488379</v>
+        <v>0.6216963263148622</v>
       </c>
       <c r="K834">
         <v>5</v>
@@ -43319,7 +43322,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43330,28 +43333,28 @@
         <v>108</v>
       </c>
       <c r="C835">
-        <v>0.03569710776418988</v>
+        <v>0.03761276525581048</v>
       </c>
       <c r="D835" t="s">
         <v>265</v>
       </c>
       <c r="E835">
-        <v>-0.3129887095892254</v>
+        <v>-0.3110615581526548</v>
       </c>
       <c r="F835">
         <v>-1</v>
       </c>
       <c r="G835">
-        <v>0.00626430289223581</v>
+        <v>0.006262387234744189</v>
       </c>
       <c r="H835">
-        <v>0.005952988709589225</v>
+        <v>0.005951061558152654</v>
       </c>
       <c r="I835">
-        <v>0.3486858173534153</v>
+        <v>0.3486743234084653</v>
       </c>
       <c r="J835">
-        <v>0.622860578447162</v>
+        <v>0.6224774469488379</v>
       </c>
       <c r="K835">
         <v>5</v>
@@ -43369,7 +43372,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43380,28 +43383,28 @@
         <v>108</v>
       </c>
       <c r="C836">
-        <v>0.02474993976449547</v>
+        <v>0.03569710776418988</v>
       </c>
       <c r="D836" t="s">
         <v>265</v>
       </c>
       <c r="E836">
-        <v>-0.3240015605969178</v>
+        <v>-0.3129887095892254</v>
       </c>
       <c r="F836">
         <v>-1</v>
       </c>
       <c r="G836">
-        <v>0.006275250060235505</v>
+        <v>0.00626430289223581</v>
       </c>
       <c r="H836">
-        <v>0.005964001560596918</v>
+        <v>0.005952988709589225</v>
       </c>
       <c r="I836">
-        <v>0.3487515003614132</v>
+        <v>0.3486858173534153</v>
       </c>
       <c r="J836">
-        <v>0.6250500120471009</v>
+        <v>0.622860578447162</v>
       </c>
       <c r="K836">
         <v>5</v>
@@ -43419,7 +43422,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43430,28 +43433,28 @@
         <v>108</v>
       </c>
       <c r="C837">
-        <v>0.01071786725750856</v>
+        <v>0.02474993976449547</v>
       </c>
       <c r="D837" t="s">
         <v>265</v>
       </c>
       <c r="E837">
-        <v>-0.3381178255389465</v>
+        <v>-0.3240015605969178</v>
       </c>
       <c r="F837">
         <v>-1</v>
       </c>
       <c r="G837">
-        <v>0.006289282132742491</v>
+        <v>0.006275250060235505</v>
       </c>
       <c r="H837">
-        <v>0.005978117825538947</v>
+        <v>0.005964001560596918</v>
       </c>
       <c r="I837">
-        <v>0.3488356927964551</v>
+        <v>0.3487515003614132</v>
       </c>
       <c r="J837">
-        <v>0.6278564265484983</v>
+        <v>0.6250500120471009</v>
       </c>
       <c r="K837">
         <v>5</v>
@@ -43469,7 +43472,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43480,28 +43483,28 @@
         <v>108</v>
       </c>
       <c r="C838">
-        <v>0.001352073833325029</v>
+        <v>0.01071786725750856</v>
       </c>
       <c r="D838" t="s">
         <v>265</v>
       </c>
       <c r="E838">
-        <v>-0.3475398137236754</v>
+        <v>-0.3381178255389465</v>
       </c>
       <c r="F838">
         <v>-1</v>
       </c>
       <c r="G838">
-        <v>0.006298647926166675</v>
+        <v>0.006289282132742491</v>
       </c>
       <c r="H838">
-        <v>0.005987539813723675</v>
+        <v>0.005978117825538947</v>
       </c>
       <c r="I838">
-        <v>0.3488918875570004</v>
+        <v>0.3488356927964551</v>
       </c>
       <c r="J838">
-        <v>0.629729585233335</v>
+        <v>0.6278564265484983</v>
       </c>
       <c r="K838">
         <v>5</v>
@@ -43519,7 +43522,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43530,28 +43533,28 @@
         <v>108</v>
       </c>
       <c r="C839">
-        <v>-0.008765444084921192</v>
+        <v>0.001352073833325029</v>
       </c>
       <c r="D839" t="s">
         <v>265</v>
       </c>
       <c r="E839">
-        <v>-0.3577180367494308</v>
+        <v>-0.3475398137236754</v>
       </c>
       <c r="F839">
         <v>-1</v>
       </c>
       <c r="G839">
-        <v>0.006308765444084921</v>
+        <v>0.006298647926166675</v>
       </c>
       <c r="H839">
-        <v>0.005997718036749431</v>
+        <v>0.005987539813723675</v>
       </c>
       <c r="I839">
-        <v>0.3489525926645096</v>
+        <v>0.3488918875570004</v>
       </c>
       <c r="J839">
-        <v>0.6317530888169842</v>
+        <v>0.629729585233335</v>
       </c>
       <c r="K839">
         <v>5</v>
@@ -43569,7 +43572,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43580,28 +43583,28 @@
         <v>108</v>
       </c>
       <c r="C840">
-        <v>-0.01826244241108999</v>
+        <v>-0.008765444084921192</v>
       </c>
       <c r="D840" t="s">
         <v>265</v>
       </c>
       <c r="E840">
-        <v>-0.3672720170655568</v>
+        <v>-0.3577180367494308</v>
       </c>
       <c r="F840">
         <v>-1</v>
       </c>
       <c r="G840">
-        <v>0.00631826244241109</v>
+        <v>0.006308765444084921</v>
       </c>
       <c r="H840">
-        <v>0.006007272017065557</v>
+        <v>0.005997718036749431</v>
       </c>
       <c r="I840">
-        <v>0.3490095746544668</v>
+        <v>0.3489525926645096</v>
       </c>
       <c r="J840">
-        <v>0.633652488482218</v>
+        <v>0.6317530888169842</v>
       </c>
       <c r="K840">
         <v>5</v>
@@ -43619,7 +43622,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43627,49 +43630,49 @@
         <v>0</v>
       </c>
       <c r="B841" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C841">
-        <v>0.1126630239428299</v>
+        <v>-0.01826244241108999</v>
       </c>
       <c r="D841" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E841">
-        <v>0.384945957779212</v>
+        <v>-0.3672720170655568</v>
       </c>
       <c r="F841">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G841">
-        <v>0.005287336976057171</v>
+        <v>0.00631826244241109</v>
       </c>
       <c r="H841">
-        <v>0.004955054042220787</v>
+        <v>0.006007272017065557</v>
       </c>
       <c r="I841">
-        <v>0.2722829338363821</v>
+        <v>0.3490095746544668</v>
       </c>
       <c r="J841">
-        <v>0.5123439556548852</v>
+        <v>0.633652488482218</v>
       </c>
       <c r="K841">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="L841">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M841">
-        <v>4.46</v>
+        <v>5.03</v>
       </c>
       <c r="N841">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="O841">
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43680,28 +43683,28 @@
         <v>111</v>
       </c>
       <c r="C842">
-        <v>0.3334339927459959</v>
+        <v>0.1126630239428299</v>
       </c>
       <c r="D842" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E842">
-        <v>0.5339826906662895</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F842">
         <v>1</v>
       </c>
       <c r="G842">
-        <v>0.005066566007254004</v>
+        <v>0.005287336976057171</v>
       </c>
       <c r="H842">
-        <v>0.00468601730933371</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I842">
-        <v>0.2005486979202935</v>
+        <v>0.2561719778274427</v>
       </c>
       <c r="J842">
-        <v>0.4686269321295058</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K842">
         <v>5.05</v>
@@ -43710,66 +43713,66 @@
         <v>2.7</v>
       </c>
       <c r="M842">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="N842">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O842">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="843" spans="1:16">
       <c r="A843" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B843" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C843">
-        <v>0.3469472497139483</v>
+        <v>0.1280333426124765</v>
       </c>
       <c r="D843" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E843">
-        <v>0.5458368943035228</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F843">
         <v>1</v>
       </c>
       <c r="G843">
-        <v>0.005053052750286052</v>
+        <v>0.005271966657387524</v>
       </c>
       <c r="H843">
-        <v>0.004674163105696478</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I843">
-        <v>0.1988896445895745</v>
+        <v>0.2408016591577962</v>
       </c>
       <c r="J843">
-        <v>0.4659510396606044</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K843">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="L843">
         <v>2.7</v>
       </c>
       <c r="M843">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="N843">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O843">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43780,28 +43783,28 @@
         <v>111</v>
       </c>
       <c r="C844">
-        <v>0.351648458141776</v>
+        <v>0.3334339927459959</v>
       </c>
       <c r="D844" t="s">
         <v>270</v>
       </c>
       <c r="E844">
-        <v>0.5499609246669439</v>
+        <v>0.5486689599875847</v>
       </c>
       <c r="F844">
         <v>1</v>
       </c>
       <c r="G844">
-        <v>0.005048351541858224</v>
+        <v>0.005066566007254004</v>
       </c>
       <c r="H844">
-        <v>0.004670039075333057</v>
+        <v>0.004691331040012415</v>
       </c>
       <c r="I844">
-        <v>0.1983124665251679</v>
+        <v>0.2152349672415887</v>
       </c>
       <c r="J844">
-        <v>0.4650201072986582</v>
+        <v>0.4686269321295058</v>
       </c>
       <c r="K844">
         <v>5.05</v>
@@ -43810,16 +43813,16 @@
         <v>2.7</v>
       </c>
       <c r="M844">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="N844">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="O844">
         <v>0</v>
       </c>
       <c r="P844" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43830,28 +43833,28 @@
         <v>111</v>
       </c>
       <c r="C845">
-        <v>0.3567649219326281</v>
+        <v>0.3469472497139483</v>
       </c>
       <c r="D845" t="s">
         <v>270</v>
       </c>
       <c r="E845">
-        <v>0.5544492285468396</v>
+        <v>0.5604964047001291</v>
       </c>
       <c r="F845">
         <v>1</v>
       </c>
       <c r="G845">
-        <v>0.005043235078067372</v>
+        <v>0.005053052750286052</v>
       </c>
       <c r="H845">
-        <v>0.004665550771453161</v>
+        <v>0.004679503595299871</v>
       </c>
       <c r="I845">
-        <v>0.1976843066142115</v>
+        <v>0.2135491549861808</v>
       </c>
       <c r="J845">
-        <v>0.4640069461519549</v>
+        <v>0.4659510396606044</v>
       </c>
       <c r="K845">
         <v>5.05</v>
@@ -43860,16 +43863,166 @@
         <v>2.7</v>
       </c>
       <c r="M845">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="N845">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="O845">
         <v>0</v>
       </c>
       <c r="P845" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="846" spans="1:16">
+      <c r="A846" s="1">
+        <v>0</v>
+      </c>
+      <c r="B846" t="s">
+        <v>111</v>
+      </c>
+      <c r="C846">
+        <v>0.351648458141776</v>
+      </c>
+      <c r="D846" t="s">
+        <v>270</v>
+      </c>
+      <c r="E846">
+        <v>0.5646111257399307</v>
+      </c>
+      <c r="F846">
+        <v>1</v>
+      </c>
+      <c r="G846">
+        <v>0.005048351541858224</v>
+      </c>
+      <c r="H846">
+        <v>0.00467538887426007</v>
+      </c>
+      <c r="I846">
+        <v>0.2129626675981546</v>
+      </c>
+      <c r="J846">
+        <v>0.4650201072986582</v>
+      </c>
+      <c r="K846">
+        <v>5.05</v>
+      </c>
+      <c r="L846">
+        <v>2.7</v>
+      </c>
+      <c r="M846">
+        <v>4.42</v>
+      </c>
+      <c r="N846">
+        <v>2.62</v>
+      </c>
+      <c r="O846">
+        <v>0</v>
+      </c>
+      <c r="P846" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="847" spans="1:16">
+      <c r="A847" s="1">
+        <v>0</v>
+      </c>
+      <c r="B847" t="s">
+        <v>111</v>
+      </c>
+      <c r="C847">
+        <v>0.3567649219326281</v>
+      </c>
+      <c r="D847" t="s">
+        <v>270</v>
+      </c>
+      <c r="E847">
+        <v>0.5690892980083593</v>
+      </c>
+      <c r="F847">
+        <v>1</v>
+      </c>
+      <c r="G847">
+        <v>0.005043235078067372</v>
+      </c>
+      <c r="H847">
+        <v>0.004670910701991641</v>
+      </c>
+      <c r="I847">
+        <v>0.2123243760757312</v>
+      </c>
+      <c r="J847">
+        <v>0.4640069461519549</v>
+      </c>
+      <c r="K847">
+        <v>5.05</v>
+      </c>
+      <c r="L847">
+        <v>2.7</v>
+      </c>
+      <c r="M847">
+        <v>4.42</v>
+      </c>
+      <c r="N847">
+        <v>2.62</v>
+      </c>
+      <c r="O847">
+        <v>0</v>
+      </c>
+      <c r="P847" t="s">
         <v>612</v>
+      </c>
+    </row>
+    <row r="848" spans="1:16">
+      <c r="A848" s="1">
+        <v>0</v>
+      </c>
+      <c r="B848" t="s">
+        <v>111</v>
+      </c>
+      <c r="C848">
+        <v>0.3589258596081755</v>
+      </c>
+      <c r="D848" t="s">
+        <v>270</v>
+      </c>
+      <c r="E848">
+        <v>0.5709806533600266</v>
+      </c>
+      <c r="F848">
+        <v>1</v>
+      </c>
+      <c r="G848">
+        <v>0.005041074140391824</v>
+      </c>
+      <c r="H848">
+        <v>0.004669019346639974</v>
+      </c>
+      <c r="I848">
+        <v>0.2120547937518511</v>
+      </c>
+      <c r="J848">
+        <v>0.4635790377013514</v>
+      </c>
+      <c r="K848">
+        <v>5.05</v>
+      </c>
+      <c r="L848">
+        <v>2.7</v>
+      </c>
+      <c r="M848">
+        <v>4.42</v>
+      </c>
+      <c r="N848">
+        <v>2.62</v>
+      </c>
+      <c r="O848">
+        <v>0</v>
+      </c>
+      <c r="P848" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-1398-1288-800.xlsx
+++ b/s60_signal/position-1398-1288-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="614">
   <si>
     <t>trade_time</t>
   </si>
@@ -823,7 +823,7 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2011-05-05</t>
@@ -2213,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P850"/>
+  <dimension ref="A1:P851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -43186,10 +43186,10 @@
         <v>-0.4367748410424306</v>
       </c>
       <c r="D832" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E832">
-        <v>-0.2031631692057423</v>
+        <v>-0.1634716865753676</v>
       </c>
       <c r="F832">
         <v>1</v>
@@ -43198,10 +43198,10 @@
         <v>0.00583677484104243</v>
       </c>
       <c r="H832">
-        <v>0.005623163169205743</v>
+        <v>0.005563471686575368</v>
       </c>
       <c r="I832">
-        <v>0.2336116718366883</v>
+        <v>0.273303154467063</v>
       </c>
       <c r="J832">
         <v>0.6211435328796893</v>
@@ -43213,10 +43213,10 @@
         <v>2.7</v>
       </c>
       <c r="M832">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N832">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O832">
         <v>1</v>
@@ -43577,52 +43577,52 @@
     </row>
     <row r="840" spans="1:16">
       <c r="A840" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B840" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C840">
-        <v>0.01071786725750856</v>
+        <v>-0.4565025608378592</v>
       </c>
       <c r="D840" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E840">
-        <v>-0.3381178255389465</v>
+        <v>-0.2214845565009029</v>
       </c>
       <c r="F840">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G840">
-        <v>0.006289282132742491</v>
+        <v>0.00585650256083786</v>
       </c>
       <c r="H840">
-        <v>0.005978117825538947</v>
+        <v>0.005641484556500902</v>
       </c>
       <c r="I840">
-        <v>0.3488356927964551</v>
+        <v>0.2350180043369563</v>
       </c>
       <c r="J840">
-        <v>0.6278564265484983</v>
+        <v>0.6250500120471009</v>
       </c>
       <c r="K840">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="L840">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="M840">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="N840">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="O840">
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43633,28 +43633,28 @@
         <v>108</v>
       </c>
       <c r="C841">
-        <v>0.001352073833325029</v>
+        <v>0.01071786725750856</v>
       </c>
       <c r="D841" t="s">
         <v>264</v>
       </c>
       <c r="E841">
-        <v>-0.3475398137236754</v>
+        <v>-0.3381178255389465</v>
       </c>
       <c r="F841">
         <v>-1</v>
       </c>
       <c r="G841">
-        <v>0.006298647926166675</v>
+        <v>0.006289282132742491</v>
       </c>
       <c r="H841">
-        <v>0.005987539813723675</v>
+        <v>0.005978117825538947</v>
       </c>
       <c r="I841">
-        <v>0.3488918875570004</v>
+        <v>0.3488356927964551</v>
       </c>
       <c r="J841">
-        <v>0.629729585233335</v>
+        <v>0.6278564265484983</v>
       </c>
       <c r="K841">
         <v>5</v>
@@ -43672,7 +43672,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43683,28 +43683,28 @@
         <v>108</v>
       </c>
       <c r="C842">
-        <v>-0.008765444084921192</v>
+        <v>0.001352073833325029</v>
       </c>
       <c r="D842" t="s">
         <v>264</v>
       </c>
       <c r="E842">
-        <v>-0.3577180367494308</v>
+        <v>-0.3475398137236754</v>
       </c>
       <c r="F842">
         <v>-1</v>
       </c>
       <c r="G842">
-        <v>0.006308765444084921</v>
+        <v>0.006298647926166675</v>
       </c>
       <c r="H842">
-        <v>0.005997718036749431</v>
+        <v>0.005987539813723675</v>
       </c>
       <c r="I842">
-        <v>0.3489525926645096</v>
+        <v>0.3488918875570004</v>
       </c>
       <c r="J842">
-        <v>0.6317530888169842</v>
+        <v>0.629729585233335</v>
       </c>
       <c r="K842">
         <v>5</v>
@@ -43722,7 +43722,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43733,28 +43733,28 @@
         <v>108</v>
       </c>
       <c r="C843">
-        <v>-0.01826244241108999</v>
+        <v>-0.008765444084921192</v>
       </c>
       <c r="D843" t="s">
         <v>264</v>
       </c>
       <c r="E843">
-        <v>-0.3672720170655568</v>
+        <v>-0.3577180367494308</v>
       </c>
       <c r="F843">
         <v>-1</v>
       </c>
       <c r="G843">
-        <v>0.00631826244241109</v>
+        <v>0.006308765444084921</v>
       </c>
       <c r="H843">
-        <v>0.006007272017065557</v>
+        <v>0.005997718036749431</v>
       </c>
       <c r="I843">
-        <v>0.3490095746544668</v>
+        <v>0.3489525926645096</v>
       </c>
       <c r="J843">
-        <v>0.633652488482218</v>
+        <v>0.6317530888169842</v>
       </c>
       <c r="K843">
         <v>5</v>
@@ -43772,7 +43772,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43780,49 +43780,49 @@
         <v>0</v>
       </c>
       <c r="B844" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C844">
-        <v>0.1126630239428299</v>
+        <v>-0.01826244241108999</v>
       </c>
       <c r="D844" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E844">
-        <v>0.3688350017702726</v>
+        <v>-0.3672720170655568</v>
       </c>
       <c r="F844">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G844">
-        <v>0.005287336976057171</v>
+        <v>0.00631826244241109</v>
       </c>
       <c r="H844">
-        <v>0.005031164998229727</v>
+        <v>0.006007272017065557</v>
       </c>
       <c r="I844">
-        <v>0.2561719778274427</v>
+        <v>0.3490095746544668</v>
       </c>
       <c r="J844">
-        <v>0.5123439556548852</v>
+        <v>0.633652488482218</v>
       </c>
       <c r="K844">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="L844">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M844">
-        <v>4.55</v>
+        <v>5.03</v>
       </c>
       <c r="N844">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O844">
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43833,28 +43833,28 @@
         <v>111</v>
       </c>
       <c r="C845">
-        <v>0.3334339927459959</v>
+        <v>0.1126630239428299</v>
       </c>
       <c r="D845" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E845">
-        <v>0.57147284523665</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F845">
         <v>1</v>
       </c>
       <c r="G845">
-        <v>0.005066566007254004</v>
+        <v>0.005287336976057171</v>
       </c>
       <c r="H845">
-        <v>0.00464852715476335</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I845">
-        <v>0.238038852490654</v>
+        <v>0.2561719778274427</v>
       </c>
       <c r="J845">
-        <v>0.4686269321295058</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K845">
         <v>5.05</v>
@@ -43863,16 +43863,16 @@
         <v>2.7</v>
       </c>
       <c r="M845">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="N845">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O845">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43883,28 +43883,28 @@
         <v>111</v>
       </c>
       <c r="C846">
-        <v>0.3469472497139483</v>
+        <v>0.3334339927459959</v>
       </c>
       <c r="D846" t="s">
         <v>269</v>
       </c>
       <c r="E846">
-        <v>0.5831129774763713</v>
+        <v>0.5655316532005346</v>
       </c>
       <c r="F846">
         <v>1</v>
       </c>
       <c r="G846">
-        <v>0.005053052750286052</v>
+        <v>0.005066566007254004</v>
       </c>
       <c r="H846">
-        <v>0.004636887022523629</v>
+        <v>0.004614468346799465</v>
       </c>
       <c r="I846">
-        <v>0.236165727762423</v>
+        <v>0.2320976604545386</v>
       </c>
       <c r="J846">
-        <v>0.4659510396606044</v>
+        <v>0.4686269321295058</v>
       </c>
       <c r="K846">
         <v>5.05</v>
@@ -43913,16 +43913,16 @@
         <v>2.7</v>
       </c>
       <c r="M846">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N846">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="O846">
         <v>0</v>
       </c>
       <c r="P846" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43933,28 +43933,28 @@
         <v>111</v>
       </c>
       <c r="C847">
-        <v>0.351648458141776</v>
+        <v>0.3469472497139483</v>
       </c>
       <c r="D847" t="s">
         <v>269</v>
       </c>
       <c r="E847">
-        <v>0.5871625332508366</v>
+        <v>0.577091508666189</v>
       </c>
       <c r="F847">
         <v>1</v>
       </c>
       <c r="G847">
-        <v>0.005048351541858224</v>
+        <v>0.005053052750286052</v>
       </c>
       <c r="H847">
-        <v>0.004632837466749164</v>
+        <v>0.004602908491333811</v>
       </c>
       <c r="I847">
-        <v>0.2355140751090605</v>
+        <v>0.2301442589522407</v>
       </c>
       <c r="J847">
-        <v>0.4650201072986582</v>
+        <v>0.4659510396606044</v>
       </c>
       <c r="K847">
         <v>5.05</v>
@@ -43963,16 +43963,16 @@
         <v>2.7</v>
       </c>
       <c r="M847">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N847">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="O847">
         <v>0</v>
       </c>
       <c r="P847" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43983,28 +43983,28 @@
         <v>111</v>
       </c>
       <c r="C848">
-        <v>0.3567649219326281</v>
+        <v>0.351648458141776</v>
       </c>
       <c r="D848" t="s">
         <v>269</v>
       </c>
       <c r="E848">
-        <v>0.5915697842389962</v>
+        <v>0.5811131364697961</v>
       </c>
       <c r="F848">
         <v>1</v>
       </c>
       <c r="G848">
-        <v>0.005043235078067372</v>
+        <v>0.005048351541858224</v>
       </c>
       <c r="H848">
-        <v>0.004628430215761004</v>
+        <v>0.004598886863530204</v>
       </c>
       <c r="I848">
-        <v>0.2348048623063681</v>
+        <v>0.2294646783280201</v>
       </c>
       <c r="J848">
-        <v>0.4640069461519549</v>
+        <v>0.4650201072986582</v>
       </c>
       <c r="K848">
         <v>5.05</v>
@@ -44013,16 +44013,16 @@
         <v>2.7</v>
       </c>
       <c r="M848">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N848">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="O848">
         <v>0</v>
       </c>
       <c r="P848" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44033,28 +44033,28 @@
         <v>111</v>
       </c>
       <c r="C849">
-        <v>0.3589258596081755</v>
+        <v>0.3567649219326281</v>
       </c>
       <c r="D849" t="s">
         <v>269</v>
       </c>
       <c r="E849">
-        <v>0.5934311859991213</v>
+        <v>0.5854899926235544</v>
       </c>
       <c r="F849">
         <v>1</v>
       </c>
       <c r="G849">
-        <v>0.005041074140391824</v>
+        <v>0.005043235078067372</v>
       </c>
       <c r="H849">
-        <v>0.004626568814000878</v>
+        <v>0.004594510007376446</v>
       </c>
       <c r="I849">
-        <v>0.2345053263909458</v>
+        <v>0.2287250706909263</v>
       </c>
       <c r="J849">
-        <v>0.4635790377013514</v>
+        <v>0.4640069461519549</v>
       </c>
       <c r="K849">
         <v>5.05</v>
@@ -44063,16 +44063,16 @@
         <v>2.7</v>
       </c>
       <c r="M849">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N849">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="O849">
         <v>0</v>
       </c>
       <c r="P849" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44083,28 +44083,28 @@
         <v>111</v>
       </c>
       <c r="C850">
-        <v>0.3582480273744801</v>
+        <v>0.3589258596081755</v>
       </c>
       <c r="D850" t="s">
         <v>269</v>
       </c>
       <c r="E850">
-        <v>0.5928473107087102</v>
+        <v>0.5873385571301615</v>
       </c>
       <c r="F850">
         <v>1</v>
       </c>
       <c r="G850">
-        <v>0.005041751972625521</v>
+        <v>0.005041074140391824</v>
       </c>
       <c r="H850">
-        <v>0.00462715268929129</v>
+        <v>0.004592661442869839</v>
       </c>
       <c r="I850">
-        <v>0.2345992833342301</v>
+        <v>0.228412697521986</v>
       </c>
       <c r="J850">
-        <v>0.4637132619060436</v>
+        <v>0.4635790377013514</v>
       </c>
       <c r="K850">
         <v>5.05</v>
@@ -44113,15 +44113,65 @@
         <v>2.7</v>
       </c>
       <c r="M850">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N850">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="O850">
         <v>0</v>
       </c>
       <c r="P850" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="851" spans="1:16">
+      <c r="A851" s="1">
+        <v>0</v>
+      </c>
+      <c r="B851" t="s">
+        <v>111</v>
+      </c>
+      <c r="C851">
+        <v>0.3582480273744801</v>
+      </c>
+      <c r="D851" t="s">
+        <v>269</v>
+      </c>
+      <c r="E851">
+        <v>0.5867587085658914</v>
+      </c>
+      <c r="F851">
+        <v>1</v>
+      </c>
+      <c r="G851">
+        <v>0.005041751972625521</v>
+      </c>
+      <c r="H851">
+        <v>0.004593241291434108</v>
+      </c>
+      <c r="I851">
+        <v>0.2285106811914113</v>
+      </c>
+      <c r="J851">
+        <v>0.4637132619060436</v>
+      </c>
+      <c r="K851">
+        <v>5.05</v>
+      </c>
+      <c r="L851">
+        <v>2.7</v>
+      </c>
+      <c r="M851">
+        <v>4.32</v>
+      </c>
+      <c r="N851">
+        <v>2.59</v>
+      </c>
+      <c r="O851">
+        <v>0</v>
+      </c>
+      <c r="P851" t="s">
         <v>613</v>
       </c>
     </row>

--- a/s60_signal/position-1398-1288-800.xlsx
+++ b/s60_signal/position-1398-1288-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="614">
   <si>
     <t>trade_time</t>
   </si>
@@ -823,7 +823,7 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2011-05-05</t>
@@ -2213,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P851"/>
+  <dimension ref="A1:P852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -42080,10 +42080,10 @@
         <v>1</v>
       </c>
       <c r="B810" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C810">
-        <v>-0.2602524537536164</v>
+        <v>-0.2302524537536166</v>
       </c>
       <c r="D810" t="s">
         <v>266</v>
@@ -42095,13 +42095,13 @@
         <v>1</v>
       </c>
       <c r="G810">
-        <v>0.005660252453753616</v>
+        <v>0.005690252453753617</v>
       </c>
       <c r="H810">
         <v>0.005402329467683995</v>
       </c>
       <c r="I810">
-        <v>0.2579229860696217</v>
+        <v>0.2279229860696219</v>
       </c>
       <c r="J810">
         <v>0.5861886047036865</v>
@@ -42110,7 +42110,7 @@
         <v>5.05</v>
       </c>
       <c r="L810">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="M810">
         <v>4.61</v>
@@ -43286,10 +43286,10 @@
         <v>-0.4395664478900536</v>
       </c>
       <c r="D834" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E834">
-        <v>-0.2057557704167032</v>
+        <v>-0.1660200643115144</v>
       </c>
       <c r="F834">
         <v>1</v>
@@ -43298,10 +43298,10 @@
         <v>0.005839566447890054</v>
       </c>
       <c r="H834">
-        <v>0.005625755770416703</v>
+        <v>0.005566020064311514</v>
       </c>
       <c r="I834">
-        <v>0.2338106774733504</v>
+        <v>0.2735463835785392</v>
       </c>
       <c r="J834">
         <v>0.6216963263148622</v>
@@ -43313,10 +43313,10 @@
         <v>2.7</v>
       </c>
       <c r="M834">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N834">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O834">
         <v>1</v>
@@ -43386,10 +43386,10 @@
         <v>-0.4435111070916311</v>
       </c>
       <c r="D836" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E836">
-        <v>-0.2094192261900494</v>
+        <v>-0.1696210304341426</v>
       </c>
       <c r="F836">
         <v>1</v>
@@ -43398,10 +43398,10 @@
         <v>0.005843511107091631</v>
       </c>
       <c r="H836">
-        <v>0.005629419226190049</v>
+        <v>0.005569621030434143</v>
       </c>
       <c r="I836">
-        <v>0.2340918809015817</v>
+        <v>0.2738900766574885</v>
       </c>
       <c r="J836">
         <v>0.6224774469488379</v>
@@ -43413,10 +43413,10 @@
         <v>2.7</v>
       </c>
       <c r="M836">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N836">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O836">
         <v>1</v>
@@ -43486,10 +43486,10 @@
         <v>-0.4454459211581678</v>
       </c>
       <c r="D838" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E838">
-        <v>-0.2112161129171897</v>
+        <v>-0.1713872666414171</v>
       </c>
       <c r="F838">
         <v>1</v>
@@ -43498,10 +43498,10 @@
         <v>0.005845445921158168</v>
       </c>
       <c r="H838">
-        <v>0.00563121611291719</v>
+        <v>0.005571387266641418</v>
       </c>
       <c r="I838">
-        <v>0.2342298082409782</v>
+        <v>0.2740586545167507</v>
       </c>
       <c r="J838">
         <v>0.622860578447162</v>
@@ -43513,10 +43513,10 @@
         <v>2.7</v>
       </c>
       <c r="M838">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N838">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O838">
         <v>1</v>
@@ -43677,52 +43677,52 @@
     </row>
     <row r="842" spans="1:16">
       <c r="A842" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B842" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C842">
-        <v>0.001352073833325029</v>
+        <v>-0.4706749540699158</v>
       </c>
       <c r="D842" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E842">
-        <v>-0.3475398137236754</v>
+        <v>-0.2346466405124565</v>
       </c>
       <c r="F842">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G842">
-        <v>0.006298647926166675</v>
+        <v>0.005870674954069916</v>
       </c>
       <c r="H842">
-        <v>0.005987539813723675</v>
+        <v>0.005654646640512457</v>
       </c>
       <c r="I842">
-        <v>0.3488918875570004</v>
+        <v>0.2360283135574592</v>
       </c>
       <c r="J842">
-        <v>0.629729585233335</v>
+        <v>0.6278564265484983</v>
       </c>
       <c r="K842">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="L842">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="M842">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="N842">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="O842">
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43733,28 +43733,28 @@
         <v>108</v>
       </c>
       <c r="C843">
-        <v>-0.008765444084921192</v>
+        <v>0.001352073833325029</v>
       </c>
       <c r="D843" t="s">
         <v>264</v>
       </c>
       <c r="E843">
-        <v>-0.3577180367494308</v>
+        <v>-0.3475398137236754</v>
       </c>
       <c r="F843">
         <v>-1</v>
       </c>
       <c r="G843">
-        <v>0.006308765444084921</v>
+        <v>0.006298647926166675</v>
       </c>
       <c r="H843">
-        <v>0.005997718036749431</v>
+        <v>0.005987539813723675</v>
       </c>
       <c r="I843">
-        <v>0.3489525926645096</v>
+        <v>0.3488918875570004</v>
       </c>
       <c r="J843">
-        <v>0.6317530888169842</v>
+        <v>0.629729585233335</v>
       </c>
       <c r="K843">
         <v>5</v>
@@ -43772,7 +43772,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43783,28 +43783,28 @@
         <v>108</v>
       </c>
       <c r="C844">
-        <v>-0.01826244241108999</v>
+        <v>-0.008765444084921192</v>
       </c>
       <c r="D844" t="s">
         <v>264</v>
       </c>
       <c r="E844">
-        <v>-0.3672720170655568</v>
+        <v>-0.3577180367494308</v>
       </c>
       <c r="F844">
         <v>-1</v>
       </c>
       <c r="G844">
-        <v>0.00631826244241109</v>
+        <v>0.006308765444084921</v>
       </c>
       <c r="H844">
-        <v>0.006007272017065557</v>
+        <v>0.005997718036749431</v>
       </c>
       <c r="I844">
-        <v>0.3490095746544668</v>
+        <v>0.3489525926645096</v>
       </c>
       <c r="J844">
-        <v>0.633652488482218</v>
+        <v>0.6317530888169842</v>
       </c>
       <c r="K844">
         <v>5</v>
@@ -43822,7 +43822,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43830,49 +43830,49 @@
         <v>0</v>
       </c>
       <c r="B845" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C845">
-        <v>0.1126630239428299</v>
+        <v>-0.01826244241108999</v>
       </c>
       <c r="D845" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E845">
-        <v>0.3688350017702726</v>
+        <v>-0.3672720170655568</v>
       </c>
       <c r="F845">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G845">
-        <v>0.005287336976057171</v>
+        <v>0.00631826244241109</v>
       </c>
       <c r="H845">
-        <v>0.005031164998229727</v>
+        <v>0.006007272017065557</v>
       </c>
       <c r="I845">
-        <v>0.2561719778274427</v>
+        <v>0.3490095746544668</v>
       </c>
       <c r="J845">
-        <v>0.5123439556548852</v>
+        <v>0.633652488482218</v>
       </c>
       <c r="K845">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="L845">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M845">
-        <v>4.55</v>
+        <v>5.03</v>
       </c>
       <c r="N845">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O845">
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43883,28 +43883,28 @@
         <v>111</v>
       </c>
       <c r="C846">
-        <v>0.3334339927459959</v>
+        <v>0.1126630239428299</v>
       </c>
       <c r="D846" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E846">
-        <v>0.5655316532005346</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F846">
         <v>1</v>
       </c>
       <c r="G846">
-        <v>0.005066566007254004</v>
+        <v>0.005287336976057171</v>
       </c>
       <c r="H846">
-        <v>0.004614468346799465</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I846">
-        <v>0.2320976604545386</v>
+        <v>0.2561719778274427</v>
       </c>
       <c r="J846">
-        <v>0.4686269321295058</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K846">
         <v>5.05</v>
@@ -43913,16 +43913,16 @@
         <v>2.7</v>
       </c>
       <c r="M846">
-        <v>4.32</v>
+        <v>4.55</v>
       </c>
       <c r="N846">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="O846">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43933,28 +43933,28 @@
         <v>111</v>
       </c>
       <c r="C847">
-        <v>0.3469472497139483</v>
+        <v>0.3334339927459959</v>
       </c>
       <c r="D847" t="s">
         <v>269</v>
       </c>
       <c r="E847">
-        <v>0.577091508666189</v>
+        <v>0.59147284523665</v>
       </c>
       <c r="F847">
         <v>1</v>
       </c>
       <c r="G847">
-        <v>0.005053052750286052</v>
+        <v>0.005066566007254004</v>
       </c>
       <c r="H847">
-        <v>0.004602908491333811</v>
+        <v>0.00466852715476335</v>
       </c>
       <c r="I847">
-        <v>0.2301442589522407</v>
+        <v>0.2580388524906541</v>
       </c>
       <c r="J847">
-        <v>0.4659510396606044</v>
+        <v>0.4686269321295058</v>
       </c>
       <c r="K847">
         <v>5.05</v>
@@ -43963,16 +43963,16 @@
         <v>2.7</v>
       </c>
       <c r="M847">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="N847">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O847">
         <v>0</v>
       </c>
       <c r="P847" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43983,28 +43983,28 @@
         <v>111</v>
       </c>
       <c r="C848">
-        <v>0.351648458141776</v>
+        <v>0.3469472497139483</v>
       </c>
       <c r="D848" t="s">
         <v>269</v>
       </c>
       <c r="E848">
-        <v>0.5811131364697961</v>
+        <v>0.6031129774763713</v>
       </c>
       <c r="F848">
         <v>1</v>
       </c>
       <c r="G848">
-        <v>0.005048351541858224</v>
+        <v>0.005053052750286052</v>
       </c>
       <c r="H848">
-        <v>0.004598886863530204</v>
+        <v>0.004656887022523629</v>
       </c>
       <c r="I848">
-        <v>0.2294646783280201</v>
+        <v>0.256165727762423</v>
       </c>
       <c r="J848">
-        <v>0.4650201072986582</v>
+        <v>0.4659510396606044</v>
       </c>
       <c r="K848">
         <v>5.05</v>
@@ -44013,16 +44013,16 @@
         <v>2.7</v>
       </c>
       <c r="M848">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="N848">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O848">
         <v>0</v>
       </c>
       <c r="P848" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44033,28 +44033,28 @@
         <v>111</v>
       </c>
       <c r="C849">
-        <v>0.3567649219326281</v>
+        <v>0.351648458141776</v>
       </c>
       <c r="D849" t="s">
         <v>269</v>
       </c>
       <c r="E849">
-        <v>0.5854899926235544</v>
+        <v>0.6071625332508366</v>
       </c>
       <c r="F849">
         <v>1</v>
       </c>
       <c r="G849">
-        <v>0.005043235078067372</v>
+        <v>0.005048351541858224</v>
       </c>
       <c r="H849">
-        <v>0.004594510007376446</v>
+        <v>0.004652837466749164</v>
       </c>
       <c r="I849">
-        <v>0.2287250706909263</v>
+        <v>0.2555140751090605</v>
       </c>
       <c r="J849">
-        <v>0.4640069461519549</v>
+        <v>0.4650201072986582</v>
       </c>
       <c r="K849">
         <v>5.05</v>
@@ -44063,16 +44063,16 @@
         <v>2.7</v>
       </c>
       <c r="M849">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="N849">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O849">
         <v>0</v>
       </c>
       <c r="P849" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44083,28 +44083,28 @@
         <v>111</v>
       </c>
       <c r="C850">
-        <v>0.3589258596081755</v>
+        <v>0.3567649219326281</v>
       </c>
       <c r="D850" t="s">
         <v>269</v>
       </c>
       <c r="E850">
-        <v>0.5873385571301615</v>
+        <v>0.6115697842389962</v>
       </c>
       <c r="F850">
         <v>1</v>
       </c>
       <c r="G850">
-        <v>0.005041074140391824</v>
+        <v>0.005043235078067372</v>
       </c>
       <c r="H850">
-        <v>0.004592661442869839</v>
+        <v>0.004648430215761003</v>
       </c>
       <c r="I850">
-        <v>0.228412697521986</v>
+        <v>0.2548048623063681</v>
       </c>
       <c r="J850">
-        <v>0.4635790377013514</v>
+        <v>0.4640069461519549</v>
       </c>
       <c r="K850">
         <v>5.05</v>
@@ -44113,16 +44113,16 @@
         <v>2.7</v>
       </c>
       <c r="M850">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="N850">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O850">
         <v>0</v>
       </c>
       <c r="P850" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44133,28 +44133,28 @@
         <v>111</v>
       </c>
       <c r="C851">
-        <v>0.3582480273744801</v>
+        <v>0.3589258596081755</v>
       </c>
       <c r="D851" t="s">
         <v>269</v>
       </c>
       <c r="E851">
-        <v>0.5867587085658914</v>
+        <v>0.6134311859991213</v>
       </c>
       <c r="F851">
         <v>1</v>
       </c>
       <c r="G851">
-        <v>0.005041751972625521</v>
+        <v>0.005041074140391824</v>
       </c>
       <c r="H851">
-        <v>0.004593241291434108</v>
+        <v>0.004646568814000878</v>
       </c>
       <c r="I851">
-        <v>0.2285106811914113</v>
+        <v>0.2545053263909458</v>
       </c>
       <c r="J851">
-        <v>0.4637132619060436</v>
+        <v>0.4635790377013514</v>
       </c>
       <c r="K851">
         <v>5.05</v>
@@ -44163,15 +44163,65 @@
         <v>2.7</v>
       </c>
       <c r="M851">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="N851">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O851">
         <v>0</v>
       </c>
       <c r="P851" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="852" spans="1:16">
+      <c r="A852" s="1">
+        <v>0</v>
+      </c>
+      <c r="B852" t="s">
+        <v>111</v>
+      </c>
+      <c r="C852">
+        <v>0.3582480273744801</v>
+      </c>
+      <c r="D852" t="s">
+        <v>269</v>
+      </c>
+      <c r="E852">
+        <v>0.6128473107087102</v>
+      </c>
+      <c r="F852">
+        <v>1</v>
+      </c>
+      <c r="G852">
+        <v>0.005041751972625521</v>
+      </c>
+      <c r="H852">
+        <v>0.004647152689291289</v>
+      </c>
+      <c r="I852">
+        <v>0.2545992833342301</v>
+      </c>
+      <c r="J852">
+        <v>0.4637132619060436</v>
+      </c>
+      <c r="K852">
+        <v>5.05</v>
+      </c>
+      <c r="L852">
+        <v>2.7</v>
+      </c>
+      <c r="M852">
+        <v>4.35</v>
+      </c>
+      <c r="N852">
+        <v>2.63</v>
+      </c>
+      <c r="O852">
+        <v>0</v>
+      </c>
+      <c r="P852" t="s">
         <v>613</v>
       </c>
     </row>

--- a/s60_signal/position-1398-1288-800.xlsx
+++ b/s60_signal/position-1398-1288-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="615">
   <si>
     <t>trade_time</t>
   </si>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2011-05-05</t>
@@ -2213,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P852"/>
+  <dimension ref="A1:P853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2310,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2360,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2410,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2460,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2510,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2560,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2610,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2660,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2710,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2760,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2810,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2860,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2910,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2960,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3010,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3060,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3110,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3160,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3210,7 +3213,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3260,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3310,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3360,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3410,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3460,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3510,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3560,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3610,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3660,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3710,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3760,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3810,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3860,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3910,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3960,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4010,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4060,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4110,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4160,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4210,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4260,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4310,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4360,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4410,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4460,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4510,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4560,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4610,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4660,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4710,7 +4713,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4760,7 +4763,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4810,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4860,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4910,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5060,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5110,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5160,7 +5163,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5210,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5260,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5310,7 +5313,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5360,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5410,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5460,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5510,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5560,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5610,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5660,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5710,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5760,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5810,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5860,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5910,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5960,7 +5963,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6010,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6060,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6110,7 +6113,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6160,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6210,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6260,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6310,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6360,7 +6363,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6410,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6460,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6510,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6760,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6810,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6860,7 +6863,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6910,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6960,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -7010,7 +7013,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7060,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7110,7 +7113,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7160,7 +7163,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7210,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7239,7 +7242,7 @@
         <v>3.77</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7289,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7339,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7389,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7439,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7468,7 +7471,7 @@
         <v>3.75</v>
       </c>
       <c r="P106" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7518,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7568,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7618,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7668,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7697,7 +7700,7 @@
         <v>3.68</v>
       </c>
       <c r="P111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7747,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7797,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7847,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7897,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7947,7 +7950,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7997,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8047,7 +8050,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8097,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8147,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8197,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8247,7 +8250,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8297,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8347,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8397,7 +8400,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8447,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8497,7 +8500,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8547,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8597,7 +8600,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8647,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8697,7 +8700,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8747,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8797,7 +8800,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8847,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8897,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8947,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8997,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9047,7 +9050,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9097,7 +9100,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9147,7 +9150,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9197,7 +9200,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9247,7 +9250,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9297,7 +9300,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9347,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9397,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9426,7 +9429,7 @@
         <v>2.84</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9476,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9526,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9576,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9626,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9676,7 +9679,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9726,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9776,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9826,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9876,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9926,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9976,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10026,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10076,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10126,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10155,7 +10158,7 @@
         <v>2.78</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10205,7 +10208,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10255,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10305,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10355,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10405,7 +10408,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10455,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="P167" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10505,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10555,7 +10558,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10605,7 +10608,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10655,7 +10658,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10705,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10755,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10805,7 +10808,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10855,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10905,7 +10908,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10955,7 +10958,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11005,7 +11008,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11055,7 +11058,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11105,7 +11108,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11155,7 +11158,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11205,7 +11208,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11255,7 +11258,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11305,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11355,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11405,7 +11408,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11455,7 +11458,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11505,7 +11508,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11555,7 +11558,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11605,7 +11608,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11655,7 +11658,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11705,7 +11708,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11755,7 +11758,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11805,7 +11808,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11855,7 +11858,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12005,7 +12008,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -12055,7 +12058,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12205,7 +12208,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12255,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12734,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12784,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12834,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="P215" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12884,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12913,7 +12916,7 @@
         <v>3.29</v>
       </c>
       <c r="P217" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12942,7 +12945,7 @@
         <v>3.29</v>
       </c>
       <c r="P218" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12992,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13042,7 +13045,7 @@
         <v>0</v>
       </c>
       <c r="P220" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13092,7 +13095,7 @@
         <v>0</v>
       </c>
       <c r="P221" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13142,7 +13145,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13192,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="P223" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13242,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13292,7 +13295,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13342,7 +13345,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13392,7 +13395,7 @@
         <v>0</v>
       </c>
       <c r="P227" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13442,7 +13445,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13492,7 +13495,7 @@
         <v>0</v>
       </c>
       <c r="P229" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13542,7 +13545,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13592,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="P231" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13642,7 +13645,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13692,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="P233" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13742,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13792,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13842,7 +13845,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13892,7 +13895,7 @@
         <v>0</v>
       </c>
       <c r="P237" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13942,7 +13945,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13992,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="P239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -14042,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14092,7 +14095,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14142,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14192,7 +14195,7 @@
         <v>0</v>
       </c>
       <c r="P243" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14242,7 +14245,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14292,7 +14295,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14342,7 +14345,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14371,7 +14374,7 @@
         <v>4.22</v>
       </c>
       <c r="P247" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14421,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14471,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14521,7 +14524,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14571,7 +14574,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14621,7 +14624,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14671,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14721,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14771,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14800,7 +14803,7 @@
         <v>4.35</v>
       </c>
       <c r="P256" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14829,7 +14832,7 @@
         <v>4.24</v>
       </c>
       <c r="P257" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14879,7 +14882,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14929,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14979,7 +14982,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -15029,7 +15032,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15079,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15129,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="P263" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15179,7 +15182,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15229,7 +15232,7 @@
         <v>0</v>
       </c>
       <c r="P265" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15279,7 +15282,7 @@
         <v>0</v>
       </c>
       <c r="P266" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15329,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="P267" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15379,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15429,7 +15432,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15479,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="P270" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15529,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="P271" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15579,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="P272" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15629,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="P273" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15679,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15729,7 +15732,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15779,7 +15782,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15829,7 +15832,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15879,7 +15882,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15929,7 +15932,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15979,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16329,7 +16332,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16379,7 +16382,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16429,7 +16432,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16479,7 +16482,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16529,7 +16532,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16579,7 +16582,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16629,7 +16632,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16679,7 +16682,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16729,7 +16732,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16779,7 +16782,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16829,7 +16832,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16879,7 +16882,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17529,7 +17532,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17579,7 +17582,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17629,7 +17632,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17679,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17729,7 +17732,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17779,7 +17782,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17829,7 +17832,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17879,7 +17882,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17929,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17979,7 +17982,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18029,7 +18032,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18079,7 +18082,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18129,7 +18132,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18179,7 +18182,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18229,7 +18232,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18279,7 +18282,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18329,7 +18332,7 @@
         <v>0</v>
       </c>
       <c r="P327" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18379,7 +18382,7 @@
         <v>0</v>
       </c>
       <c r="P328" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18429,7 +18432,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18479,7 +18482,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18529,7 +18532,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18579,7 +18582,7 @@
         <v>0</v>
       </c>
       <c r="P332" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18629,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="P333" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18679,7 +18682,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18729,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18779,7 +18782,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18829,7 +18832,7 @@
         <v>0</v>
       </c>
       <c r="P337" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18879,7 +18882,7 @@
         <v>0</v>
       </c>
       <c r="P338" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18929,7 +18932,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18979,7 +18982,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19029,7 +19032,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19079,7 +19082,7 @@
         <v>0</v>
       </c>
       <c r="P342" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19129,7 +19132,7 @@
         <v>0</v>
       </c>
       <c r="P343" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19179,7 +19182,7 @@
         <v>0</v>
       </c>
       <c r="P344" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19229,7 +19232,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19279,7 +19282,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19329,7 +19332,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19379,7 +19382,7 @@
         <v>0</v>
       </c>
       <c r="P348" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19429,7 +19432,7 @@
         <v>0</v>
       </c>
       <c r="P349" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19479,7 +19482,7 @@
         <v>0</v>
       </c>
       <c r="P350" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19779,7 +19782,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19829,7 +19832,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19879,7 +19882,7 @@
         <v>0</v>
       </c>
       <c r="P358" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19929,7 +19932,7 @@
         <v>0</v>
       </c>
       <c r="P359" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19979,7 +19982,7 @@
         <v>0</v>
       </c>
       <c r="P360" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20029,7 +20032,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20079,7 +20082,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20129,7 +20132,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20179,7 +20182,7 @@
         <v>0</v>
       </c>
       <c r="P364" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20229,7 +20232,7 @@
         <v>0</v>
       </c>
       <c r="P365" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20279,7 +20282,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20329,7 +20332,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20379,7 +20382,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20429,7 +20432,7 @@
         <v>0</v>
       </c>
       <c r="P369" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20479,7 +20482,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20529,7 +20532,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20579,7 +20582,7 @@
         <v>0</v>
       </c>
       <c r="P372" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20629,7 +20632,7 @@
         <v>0</v>
       </c>
       <c r="P373" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20679,7 +20682,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20729,7 +20732,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20779,7 +20782,7 @@
         <v>0</v>
       </c>
       <c r="P376" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20829,7 +20832,7 @@
         <v>0</v>
       </c>
       <c r="P377" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21029,7 +21032,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21079,7 +21082,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21129,7 +21132,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21279,7 +21282,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21329,7 +21332,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21379,7 +21382,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21429,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="P389" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21458,7 +21461,7 @@
         <v>3.81</v>
       </c>
       <c r="P390" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21487,7 +21490,7 @@
         <v>3.89</v>
       </c>
       <c r="P391" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21537,7 +21540,7 @@
         <v>0</v>
       </c>
       <c r="P392" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21587,7 +21590,7 @@
         <v>0</v>
       </c>
       <c r="P393" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21637,7 +21640,7 @@
         <v>0</v>
       </c>
       <c r="P394" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21687,7 +21690,7 @@
         <v>0</v>
       </c>
       <c r="P395" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21737,7 +21740,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21787,7 +21790,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21837,7 +21840,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21887,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21987,7 +21990,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22137,7 +22140,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22187,7 +22190,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22237,7 +22240,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22337,7 +22340,7 @@
         <v>0</v>
       </c>
       <c r="P408" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22387,7 +22390,7 @@
         <v>0</v>
       </c>
       <c r="P409" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22416,7 +22419,7 @@
         <v>4.29</v>
       </c>
       <c r="P410" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22445,7 +22448,7 @@
         <v>4.23</v>
       </c>
       <c r="P411" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22495,7 +22498,7 @@
         <v>0</v>
       </c>
       <c r="P412" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22545,7 +22548,7 @@
         <v>0</v>
       </c>
       <c r="P413" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22595,7 +22598,7 @@
         <v>0</v>
       </c>
       <c r="P414" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22645,7 +22648,7 @@
         <v>0</v>
       </c>
       <c r="P415" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22695,7 +22698,7 @@
         <v>0</v>
       </c>
       <c r="P416" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22745,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="P417" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22795,7 +22798,7 @@
         <v>0</v>
       </c>
       <c r="P418" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22845,7 +22848,7 @@
         <v>0</v>
       </c>
       <c r="P419" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22895,7 +22898,7 @@
         <v>0</v>
       </c>
       <c r="P420" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22945,7 +22948,7 @@
         <v>0</v>
       </c>
       <c r="P421" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22995,7 +22998,7 @@
         <v>0</v>
       </c>
       <c r="P422" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23045,7 +23048,7 @@
         <v>0</v>
       </c>
       <c r="P423" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23095,7 +23098,7 @@
         <v>0</v>
       </c>
       <c r="P424" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23145,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="P425" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23195,7 +23198,7 @@
         <v>0</v>
       </c>
       <c r="P426" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23245,7 +23248,7 @@
         <v>0</v>
       </c>
       <c r="P427" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23295,7 +23298,7 @@
         <v>0</v>
       </c>
       <c r="P428" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23345,7 +23348,7 @@
         <v>0</v>
       </c>
       <c r="P429" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23374,7 +23377,7 @@
         <v>4.44</v>
       </c>
       <c r="P430" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23403,7 +23406,7 @@
         <v>4.47</v>
       </c>
       <c r="P431" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23432,7 +23435,7 @@
         <v>4.42</v>
       </c>
       <c r="P432" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23461,7 +23464,7 @@
         <v>4.22</v>
       </c>
       <c r="P433" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23490,7 +23493,7 @@
         <v>4.14</v>
       </c>
       <c r="P434" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23540,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="P435" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23590,7 +23593,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23640,7 +23643,7 @@
         <v>0</v>
       </c>
       <c r="P437" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23690,7 +23693,7 @@
         <v>0</v>
       </c>
       <c r="P438" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23740,7 +23743,7 @@
         <v>0</v>
       </c>
       <c r="P439" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23790,7 +23793,7 @@
         <v>0</v>
       </c>
       <c r="P440" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23840,7 +23843,7 @@
         <v>0</v>
       </c>
       <c r="P441" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23890,7 +23893,7 @@
         <v>0</v>
       </c>
       <c r="P442" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23940,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23990,7 +23993,7 @@
         <v>0</v>
       </c>
       <c r="P444" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24040,7 +24043,7 @@
         <v>0</v>
       </c>
       <c r="P445" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24090,7 +24093,7 @@
         <v>0</v>
       </c>
       <c r="P446" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24140,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="P447" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24190,7 +24193,7 @@
         <v>0</v>
       </c>
       <c r="P448" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24240,7 +24243,7 @@
         <v>0</v>
       </c>
       <c r="P449" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24290,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="P450" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24340,7 +24343,7 @@
         <v>0</v>
       </c>
       <c r="P451" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24390,7 +24393,7 @@
         <v>0</v>
       </c>
       <c r="P452" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24440,7 +24443,7 @@
         <v>0</v>
       </c>
       <c r="P453" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24490,7 +24493,7 @@
         <v>0</v>
       </c>
       <c r="P454" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24540,7 +24543,7 @@
         <v>0</v>
       </c>
       <c r="P455" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24590,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="P456" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24640,7 +24643,7 @@
         <v>0</v>
       </c>
       <c r="P457" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24690,7 +24693,7 @@
         <v>0</v>
       </c>
       <c r="P458" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24740,7 +24743,7 @@
         <v>0</v>
       </c>
       <c r="P459" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24790,7 +24793,7 @@
         <v>0</v>
       </c>
       <c r="P460" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24840,7 +24843,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24890,7 +24893,7 @@
         <v>0</v>
       </c>
       <c r="P462" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24940,7 +24943,7 @@
         <v>0</v>
       </c>
       <c r="P463" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24990,7 +24993,7 @@
         <v>0</v>
       </c>
       <c r="P464" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25040,7 +25043,7 @@
         <v>0</v>
       </c>
       <c r="P465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25090,7 +25093,7 @@
         <v>0</v>
       </c>
       <c r="P466" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25140,7 +25143,7 @@
         <v>0</v>
       </c>
       <c r="P467" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25190,7 +25193,7 @@
         <v>0</v>
       </c>
       <c r="P468" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25240,7 +25243,7 @@
         <v>0</v>
       </c>
       <c r="P469" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25290,7 +25293,7 @@
         <v>0</v>
       </c>
       <c r="P470" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25340,7 +25343,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25390,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25440,7 +25443,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25490,7 +25493,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25540,7 +25543,7 @@
         <v>0</v>
       </c>
       <c r="P475" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25590,7 +25593,7 @@
         <v>0</v>
       </c>
       <c r="P476" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25640,7 +25643,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25690,7 +25693,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25740,7 +25743,7 @@
         <v>0</v>
       </c>
       <c r="P479" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25790,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="P480" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25840,7 +25843,7 @@
         <v>0</v>
       </c>
       <c r="P481" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25890,7 +25893,7 @@
         <v>0</v>
       </c>
       <c r="P482" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25940,7 +25943,7 @@
         <v>0</v>
       </c>
       <c r="P483" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25990,7 +25993,7 @@
         <v>0</v>
       </c>
       <c r="P484" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26040,7 +26043,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26090,7 +26093,7 @@
         <v>0</v>
       </c>
       <c r="P486" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26140,7 +26143,7 @@
         <v>0</v>
       </c>
       <c r="P487" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26190,7 +26193,7 @@
         <v>0</v>
       </c>
       <c r="P488" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26240,7 +26243,7 @@
         <v>0</v>
       </c>
       <c r="P489" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26290,7 +26293,7 @@
         <v>0</v>
       </c>
       <c r="P490" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26340,7 +26343,7 @@
         <v>0</v>
       </c>
       <c r="P491" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26390,7 +26393,7 @@
         <v>0</v>
       </c>
       <c r="P492" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26440,7 +26443,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26490,7 +26493,7 @@
         <v>0</v>
       </c>
       <c r="P494" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26540,7 +26543,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26590,7 +26593,7 @@
         <v>0</v>
       </c>
       <c r="P496" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26640,7 +26643,7 @@
         <v>0</v>
       </c>
       <c r="P497" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26690,7 +26693,7 @@
         <v>0</v>
       </c>
       <c r="P498" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26740,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="P499" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26790,7 +26793,7 @@
         <v>0</v>
       </c>
       <c r="P500" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26840,7 +26843,7 @@
         <v>0</v>
       </c>
       <c r="P501" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26890,7 +26893,7 @@
         <v>0</v>
       </c>
       <c r="P502" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26940,7 +26943,7 @@
         <v>0</v>
       </c>
       <c r="P503" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26990,7 +26993,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27040,7 +27043,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27090,7 +27093,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27140,7 +27143,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27190,7 +27193,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27240,7 +27243,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27290,7 +27293,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27340,7 +27343,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27440,7 +27443,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27490,7 +27493,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27540,7 +27543,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27590,7 +27593,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27640,7 +27643,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27690,7 +27693,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27740,7 +27743,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27790,7 +27793,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27840,7 +27843,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27890,7 +27893,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27940,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27990,7 +27993,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28040,7 +28043,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28090,7 +28093,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28140,7 +28143,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -29590,7 +29593,7 @@
         <v>0</v>
       </c>
       <c r="P556" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29640,7 +29643,7 @@
         <v>0</v>
       </c>
       <c r="P557" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29690,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="P558" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29740,7 +29743,7 @@
         <v>0</v>
       </c>
       <c r="P559" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29790,7 +29793,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29840,7 +29843,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29890,7 +29893,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29940,7 +29943,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29990,7 +29993,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30040,7 +30043,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30090,7 +30093,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30140,7 +30143,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30169,7 +30172,7 @@
         <v>3.63</v>
       </c>
       <c r="P568" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30219,7 +30222,7 @@
         <v>0</v>
       </c>
       <c r="P569" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30248,7 +30251,7 @@
         <v>3.7</v>
       </c>
       <c r="P570" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30277,7 +30280,7 @@
         <v>3.7</v>
       </c>
       <c r="P571" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30327,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30377,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30427,7 +30430,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30477,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30527,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30577,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30627,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30677,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30727,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30777,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30827,7 +30830,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30877,7 +30880,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30927,7 +30930,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30977,7 +30980,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31027,7 +31030,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31077,7 +31080,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31177,7 +31180,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31227,7 +31230,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31277,7 +31280,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31327,7 +31330,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31377,7 +31380,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31427,7 +31430,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31477,7 +31480,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31527,7 +31530,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31577,7 +31580,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31627,7 +31630,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31677,7 +31680,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31727,7 +31730,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31877,7 +31880,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31927,7 +31930,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31977,7 +31980,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32027,7 +32030,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32077,7 +32080,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32127,7 +32130,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32156,7 +32159,7 @@
         <v>3.4</v>
       </c>
       <c r="P609" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32206,7 +32209,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32256,7 +32259,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32306,7 +32309,7 @@
         <v>0</v>
       </c>
       <c r="P612" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32356,7 +32359,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32406,7 +32409,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32456,7 +32459,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32506,7 +32509,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32556,7 +32559,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32606,7 +32609,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32656,7 +32659,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32706,7 +32709,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32756,7 +32759,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32806,7 +32809,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32856,7 +32859,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32906,7 +32909,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32956,7 +32959,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33006,7 +33009,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33056,7 +33059,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33106,7 +33109,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33156,7 +33159,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33206,7 +33209,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33256,7 +33259,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33306,7 +33309,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33356,7 +33359,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33406,7 +33409,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33456,7 +33459,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33506,7 +33509,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33706,7 +33709,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33756,7 +33759,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33806,7 +33809,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34006,7 +34009,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34056,7 +34059,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34106,7 +34109,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34156,7 +34159,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34206,7 +34209,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34256,7 +34259,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34306,7 +34309,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34356,7 +34359,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34406,7 +34409,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34435,7 +34438,7 @@
         <v>3.69</v>
       </c>
       <c r="P655" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34485,7 +34488,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34535,7 +34538,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34585,7 +34588,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34635,7 +34638,7 @@
         <v>0</v>
       </c>
       <c r="P659" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34685,7 +34688,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34735,7 +34738,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34785,7 +34788,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34835,7 +34838,7 @@
         <v>0</v>
       </c>
       <c r="P663" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34885,7 +34888,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34935,7 +34938,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34985,7 +34988,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35014,7 +35017,7 @@
         <v>3.69</v>
       </c>
       <c r="P667" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35043,7 +35046,7 @@
         <v>3.61</v>
       </c>
       <c r="P668" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35093,7 +35096,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35143,7 +35146,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35193,7 +35196,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35243,7 +35246,7 @@
         <v>0</v>
       </c>
       <c r="P672" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35293,7 +35296,7 @@
         <v>0</v>
       </c>
       <c r="P673" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35343,7 +35346,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35393,7 +35396,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35443,7 +35446,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35493,7 +35496,7 @@
         <v>0</v>
       </c>
       <c r="P677" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35543,7 +35546,7 @@
         <v>0</v>
       </c>
       <c r="P678" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35593,7 +35596,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35643,7 +35646,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35693,7 +35696,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35743,7 +35746,7 @@
         <v>0</v>
       </c>
       <c r="P682" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35793,7 +35796,7 @@
         <v>0</v>
       </c>
       <c r="P683" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35843,7 +35846,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35893,7 +35896,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35943,7 +35946,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35993,7 +35996,7 @@
         <v>0</v>
       </c>
       <c r="P687" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36043,7 +36046,7 @@
         <v>0</v>
       </c>
       <c r="P688" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36093,7 +36096,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36143,7 +36146,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36193,7 +36196,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36243,7 +36246,7 @@
         <v>0</v>
       </c>
       <c r="P692" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36293,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="P693" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36343,7 +36346,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36393,7 +36396,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36443,7 +36446,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36493,7 +36496,7 @@
         <v>0</v>
       </c>
       <c r="P697" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36543,7 +36546,7 @@
         <v>0</v>
       </c>
       <c r="P698" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36593,7 +36596,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36643,7 +36646,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36693,7 +36696,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36743,7 +36746,7 @@
         <v>0</v>
       </c>
       <c r="P702" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36793,7 +36796,7 @@
         <v>0</v>
       </c>
       <c r="P703" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36843,7 +36846,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36893,7 +36896,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36943,7 +36946,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36993,7 +36996,7 @@
         <v>0</v>
       </c>
       <c r="P707" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37043,7 +37046,7 @@
         <v>0</v>
       </c>
       <c r="P708" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37093,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37143,7 +37146,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37193,7 +37196,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37243,7 +37246,7 @@
         <v>0</v>
       </c>
       <c r="P712" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37293,7 +37296,7 @@
         <v>0</v>
       </c>
       <c r="P713" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37343,7 +37346,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37393,7 +37396,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37443,7 +37446,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37493,7 +37496,7 @@
         <v>0</v>
       </c>
       <c r="P717" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37543,7 +37546,7 @@
         <v>0</v>
       </c>
       <c r="P718" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37593,7 +37596,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37643,7 +37646,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37693,7 +37696,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37743,7 +37746,7 @@
         <v>0</v>
       </c>
       <c r="P722" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37793,7 +37796,7 @@
         <v>0</v>
       </c>
       <c r="P723" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38093,7 +38096,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38143,7 +38146,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38193,7 +38196,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38243,7 +38246,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38293,7 +38296,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38343,7 +38346,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38393,7 +38396,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38443,7 +38446,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38593,7 +38596,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38643,7 +38646,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38693,7 +38696,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38743,7 +38746,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38922,7 +38925,7 @@
         <v>0</v>
       </c>
       <c r="P746" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39022,7 +39025,7 @@
         <v>0</v>
       </c>
       <c r="P748" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39072,7 +39075,7 @@
         <v>0</v>
       </c>
       <c r="P749" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39122,7 +39125,7 @@
         <v>0</v>
       </c>
       <c r="P750" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39172,7 +39175,7 @@
         <v>0</v>
       </c>
       <c r="P751" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39222,7 +39225,7 @@
         <v>0</v>
       </c>
       <c r="P752" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39272,7 +39275,7 @@
         <v>0</v>
       </c>
       <c r="P753" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39322,7 +39325,7 @@
         <v>0</v>
       </c>
       <c r="P754" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39372,7 +39375,7 @@
         <v>0</v>
       </c>
       <c r="P755" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39422,7 +39425,7 @@
         <v>0</v>
       </c>
       <c r="P756" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39472,7 +39475,7 @@
         <v>0</v>
       </c>
       <c r="P757" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39522,7 +39525,7 @@
         <v>0</v>
       </c>
       <c r="P758" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39572,7 +39575,7 @@
         <v>0</v>
       </c>
       <c r="P759" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39622,7 +39625,7 @@
         <v>0</v>
       </c>
       <c r="P760" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39672,7 +39675,7 @@
         <v>0</v>
       </c>
       <c r="P761" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39722,7 +39725,7 @@
         <v>0</v>
       </c>
       <c r="P762" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39772,7 +39775,7 @@
         <v>0</v>
       </c>
       <c r="P763" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39822,7 +39825,7 @@
         <v>0</v>
       </c>
       <c r="P764" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -39922,7 +39925,7 @@
         <v>0</v>
       </c>
       <c r="P766" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39972,7 +39975,7 @@
         <v>0</v>
       </c>
       <c r="P767" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40022,7 +40025,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40072,7 +40075,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40122,7 +40125,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40172,7 +40175,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40222,7 +40225,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40272,7 +40275,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40322,7 +40325,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40372,7 +40375,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40422,7 +40425,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40472,7 +40475,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40522,7 +40525,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40572,7 +40575,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40622,7 +40625,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40672,7 +40675,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40722,7 +40725,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40772,7 +40775,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40822,7 +40825,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -40872,7 +40875,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -40922,7 +40925,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -40972,7 +40975,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41022,7 +41025,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41072,7 +41075,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41122,7 +41125,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41172,7 +41175,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41222,7 +41225,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41272,7 +41275,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41322,7 +41325,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41372,7 +41375,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41422,7 +41425,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41472,7 +41475,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41522,7 +41525,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41572,7 +41575,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41622,7 +41625,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41672,7 +41675,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41722,7 +41725,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41772,7 +41775,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41822,7 +41825,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41872,7 +41875,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -41922,7 +41925,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -41972,7 +41975,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42022,7 +42025,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42072,7 +42075,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42122,7 +42125,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42172,7 +42175,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42222,7 +42225,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42272,7 +42275,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42322,7 +42325,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42372,7 +42375,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42422,7 +42425,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42472,7 +42475,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42522,7 +42525,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42572,7 +42575,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42622,7 +42625,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42672,7 +42675,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42722,7 +42725,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42772,7 +42775,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42822,7 +42825,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -42872,7 +42875,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -42922,7 +42925,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -42972,7 +42975,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43022,7 +43025,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43072,7 +43075,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43122,7 +43125,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43172,7 +43175,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43222,7 +43225,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43272,7 +43275,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43322,7 +43325,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43372,7 +43375,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43422,7 +43425,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43472,7 +43475,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43522,7 +43525,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43572,7 +43575,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43586,10 +43589,10 @@
         <v>-0.4565025608378592</v>
       </c>
       <c r="D840" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E840">
-        <v>-0.2214845565009029</v>
+        <v>-0.181480555537135</v>
       </c>
       <c r="F840">
         <v>1</v>
@@ -43598,10 +43601,10 @@
         <v>0.00585650256083786</v>
       </c>
       <c r="H840">
-        <v>0.005641484556500902</v>
+        <v>0.005581480555537135</v>
       </c>
       <c r="I840">
-        <v>0.2350180043369563</v>
+        <v>0.2750220053007242</v>
       </c>
       <c r="J840">
         <v>0.6250500120471009</v>
@@ -43613,16 +43616,16 @@
         <v>2.7</v>
       </c>
       <c r="M840">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N840">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O840">
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43672,7 +43675,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43686,10 +43689,10 @@
         <v>-0.4706749540699158</v>
       </c>
       <c r="D842" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E842">
-        <v>-0.2346466405124565</v>
+        <v>-0.1944181263885771</v>
       </c>
       <c r="F842">
         <v>1</v>
@@ -43698,10 +43701,10 @@
         <v>0.005870674954069916</v>
       </c>
       <c r="H842">
-        <v>0.005654646640512457</v>
+        <v>0.005594418126388577</v>
       </c>
       <c r="I842">
-        <v>0.2360283135574592</v>
+        <v>0.2762568276813386</v>
       </c>
       <c r="J842">
         <v>0.6278564265484983</v>
@@ -43713,16 +43716,16 @@
         <v>2.7</v>
       </c>
       <c r="M842">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="N842">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O842">
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43772,51 +43775,51 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="844" spans="1:16">
       <c r="A844" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B844" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C844">
-        <v>-0.008765444084921192</v>
+        <v>-0.4801344054283416</v>
       </c>
       <c r="D844" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E844">
-        <v>-0.3577180367494308</v>
+        <v>-0.243431754744341</v>
       </c>
       <c r="F844">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G844">
-        <v>0.006308765444084921</v>
+        <v>0.005880134405428341</v>
       </c>
       <c r="H844">
-        <v>0.005997718036749431</v>
+        <v>0.005663431754744341</v>
       </c>
       <c r="I844">
-        <v>0.3489525926645096</v>
+        <v>0.2367026506840006</v>
       </c>
       <c r="J844">
-        <v>0.6317530888169842</v>
+        <v>0.629729585233335</v>
       </c>
       <c r="K844">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="L844">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="M844">
-        <v>5.03</v>
+        <v>4.69</v>
       </c>
       <c r="N844">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="O844">
         <v>1</v>
@@ -43833,28 +43836,28 @@
         <v>108</v>
       </c>
       <c r="C845">
-        <v>-0.01826244241108999</v>
+        <v>-0.008765444084921192</v>
       </c>
       <c r="D845" t="s">
         <v>264</v>
       </c>
       <c r="E845">
-        <v>-0.3672720170655568</v>
+        <v>-0.3577180367494308</v>
       </c>
       <c r="F845">
         <v>-1</v>
       </c>
       <c r="G845">
-        <v>0.00631826244241109</v>
+        <v>0.006308765444084921</v>
       </c>
       <c r="H845">
-        <v>0.006007272017065557</v>
+        <v>0.005997718036749431</v>
       </c>
       <c r="I845">
-        <v>0.3490095746544668</v>
+        <v>0.3489525926645096</v>
       </c>
       <c r="J845">
-        <v>0.633652488482218</v>
+        <v>0.6317530888169842</v>
       </c>
       <c r="K845">
         <v>5</v>
@@ -43880,43 +43883,43 @@
         <v>0</v>
       </c>
       <c r="B846" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C846">
-        <v>0.1126630239428299</v>
+        <v>-0.01826244241108999</v>
       </c>
       <c r="D846" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E846">
-        <v>0.3688350017702726</v>
+        <v>-0.3672720170655568</v>
       </c>
       <c r="F846">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G846">
-        <v>0.005287336976057171</v>
+        <v>0.00631826244241109</v>
       </c>
       <c r="H846">
-        <v>0.005031164998229727</v>
+        <v>0.006007272017065557</v>
       </c>
       <c r="I846">
-        <v>0.2561719778274427</v>
+        <v>0.3490095746544668</v>
       </c>
       <c r="J846">
-        <v>0.5123439556548852</v>
+        <v>0.633652488482218</v>
       </c>
       <c r="K846">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="L846">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M846">
-        <v>4.55</v>
+        <v>5.03</v>
       </c>
       <c r="N846">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O846">
         <v>1</v>
@@ -43933,28 +43936,28 @@
         <v>111</v>
       </c>
       <c r="C847">
-        <v>0.3334339927459959</v>
+        <v>0.1126630239428299</v>
       </c>
       <c r="D847" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E847">
-        <v>0.59147284523665</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F847">
         <v>1</v>
       </c>
       <c r="G847">
-        <v>0.005066566007254004</v>
+        <v>0.005287336976057171</v>
       </c>
       <c r="H847">
-        <v>0.00466852715476335</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I847">
-        <v>0.2580388524906541</v>
+        <v>0.2561719778274427</v>
       </c>
       <c r="J847">
-        <v>0.4686269321295058</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K847">
         <v>5.05</v>
@@ -43963,13 +43966,13 @@
         <v>2.7</v>
       </c>
       <c r="M847">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="N847">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="O847">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P847" t="s">
         <v>608</v>
@@ -43983,28 +43986,28 @@
         <v>111</v>
       </c>
       <c r="C848">
-        <v>0.3469472497139483</v>
+        <v>0.3334339927459959</v>
       </c>
       <c r="D848" t="s">
         <v>269</v>
       </c>
       <c r="E848">
-        <v>0.6031129774763713</v>
+        <v>0.59147284523665</v>
       </c>
       <c r="F848">
         <v>1</v>
       </c>
       <c r="G848">
-        <v>0.005053052750286052</v>
+        <v>0.005066566007254004</v>
       </c>
       <c r="H848">
-        <v>0.004656887022523629</v>
+        <v>0.00466852715476335</v>
       </c>
       <c r="I848">
-        <v>0.256165727762423</v>
+        <v>0.2580388524906541</v>
       </c>
       <c r="J848">
-        <v>0.4659510396606044</v>
+        <v>0.4686269321295058</v>
       </c>
       <c r="K848">
         <v>5.05</v>
@@ -44019,7 +44022,7 @@
         <v>2.63</v>
       </c>
       <c r="O848">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P848" t="s">
         <v>609</v>
@@ -44033,28 +44036,28 @@
         <v>111</v>
       </c>
       <c r="C849">
-        <v>0.351648458141776</v>
+        <v>0.3469472497139483</v>
       </c>
       <c r="D849" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E849">
-        <v>0.6071625332508366</v>
+        <v>0.561751019062795</v>
       </c>
       <c r="F849">
         <v>1</v>
       </c>
       <c r="G849">
-        <v>0.005048351541858224</v>
+        <v>0.005053052750286052</v>
       </c>
       <c r="H849">
-        <v>0.004652837466749164</v>
+        <v>0.004578248980937205</v>
       </c>
       <c r="I849">
-        <v>0.2555140751090605</v>
+        <v>0.2148037693488467</v>
       </c>
       <c r="J849">
-        <v>0.4650201072986582</v>
+        <v>0.4659510396606044</v>
       </c>
       <c r="K849">
         <v>5.05</v>
@@ -44063,10 +44066,10 @@
         <v>2.7</v>
       </c>
       <c r="M849">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="N849">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="O849">
         <v>0</v>
@@ -44083,28 +44086,28 @@
         <v>111</v>
       </c>
       <c r="C850">
-        <v>0.3567649219326281</v>
+        <v>0.351648458141776</v>
       </c>
       <c r="D850" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E850">
-        <v>0.6115697842389962</v>
+        <v>0.5657633375427831</v>
       </c>
       <c r="F850">
         <v>1</v>
       </c>
       <c r="G850">
-        <v>0.005043235078067372</v>
+        <v>0.005048351541858224</v>
       </c>
       <c r="H850">
-        <v>0.004648430215761003</v>
+        <v>0.004574236662457217</v>
       </c>
       <c r="I850">
-        <v>0.2548048623063681</v>
+        <v>0.214114879401007</v>
       </c>
       <c r="J850">
-        <v>0.4640069461519549</v>
+        <v>0.4650201072986582</v>
       </c>
       <c r="K850">
         <v>5.05</v>
@@ -44113,10 +44116,10 @@
         <v>2.7</v>
       </c>
       <c r="M850">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="N850">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="O850">
         <v>0</v>
@@ -44133,28 +44136,28 @@
         <v>111</v>
       </c>
       <c r="C851">
-        <v>0.3589258596081755</v>
+        <v>0.3567649219326281</v>
       </c>
       <c r="D851" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E851">
-        <v>0.6134311859991213</v>
+        <v>0.5701300620850742</v>
       </c>
       <c r="F851">
         <v>1</v>
       </c>
       <c r="G851">
-        <v>0.005041074140391824</v>
+        <v>0.005043235078067372</v>
       </c>
       <c r="H851">
-        <v>0.004646568814000878</v>
+        <v>0.004569869937914925</v>
       </c>
       <c r="I851">
-        <v>0.2545053263909458</v>
+        <v>0.2133651401524461</v>
       </c>
       <c r="J851">
-        <v>0.4635790377013514</v>
+        <v>0.4640069461519549</v>
       </c>
       <c r="K851">
         <v>5.05</v>
@@ -44163,10 +44166,10 @@
         <v>2.7</v>
       </c>
       <c r="M851">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="N851">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="O851">
         <v>0</v>
@@ -44183,28 +44186,28 @@
         <v>111</v>
       </c>
       <c r="C852">
-        <v>0.3582480273744801</v>
+        <v>0.3589258596081755</v>
       </c>
       <c r="D852" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E852">
-        <v>0.6128473107087102</v>
+        <v>0.5719743475071752</v>
       </c>
       <c r="F852">
         <v>1</v>
       </c>
       <c r="G852">
-        <v>0.005041751972625521</v>
+        <v>0.005041074140391824</v>
       </c>
       <c r="H852">
-        <v>0.004647152689291289</v>
+        <v>0.004568025652492824</v>
       </c>
       <c r="I852">
-        <v>0.2545992833342301</v>
+        <v>0.2130484878989998</v>
       </c>
       <c r="J852">
-        <v>0.4637132619060436</v>
+        <v>0.4635790377013514</v>
       </c>
       <c r="K852">
         <v>5.05</v>
@@ -44213,16 +44216,66 @@
         <v>2.7</v>
       </c>
       <c r="M852">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="N852">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="O852">
         <v>0</v>
       </c>
       <c r="P852" t="s">
         <v>613</v>
+      </c>
+    </row>
+    <row r="853" spans="1:16">
+      <c r="A853" s="1">
+        <v>0</v>
+      </c>
+      <c r="B853" t="s">
+        <v>111</v>
+      </c>
+      <c r="C853">
+        <v>0.3582480273744801</v>
+      </c>
+      <c r="D853" t="s">
+        <v>270</v>
+      </c>
+      <c r="E853">
+        <v>0.571395841184952</v>
+      </c>
+      <c r="F853">
+        <v>1</v>
+      </c>
+      <c r="G853">
+        <v>0.005041751972625521</v>
+      </c>
+      <c r="H853">
+        <v>0.004568604158815048</v>
+      </c>
+      <c r="I853">
+        <v>0.2131478138104719</v>
+      </c>
+      <c r="J853">
+        <v>0.4637132619060436</v>
+      </c>
+      <c r="K853">
+        <v>5.05</v>
+      </c>
+      <c r="L853">
+        <v>2.7</v>
+      </c>
+      <c r="M853">
+        <v>4.31</v>
+      </c>
+      <c r="N853">
+        <v>2.57</v>
+      </c>
+      <c r="O853">
+        <v>0</v>
+      </c>
+      <c r="P853" t="s">
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-1398-1288-800.xlsx
+++ b/s60_signal/position-1398-1288-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="614">
   <si>
     <t>trade_time</t>
   </si>
@@ -824,9 +824,6 @@
   </si>
   <si>
     <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
   </si>
   <si>
     <t>2011-05-05</t>
@@ -2216,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P853"/>
+  <dimension ref="A1:P852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2313,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2363,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2413,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2463,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2513,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2563,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2613,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2663,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2713,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2763,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2813,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2863,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2913,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2963,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3013,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3063,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3113,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3163,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3213,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3263,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3313,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3363,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3413,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3463,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3513,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3563,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3613,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3663,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3713,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3763,7 +3760,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3813,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3863,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3913,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3963,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4013,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4063,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4113,7 +4110,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4163,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4213,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4263,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4313,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4363,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4413,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4463,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4513,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4563,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4613,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4663,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4713,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4763,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4813,7 +4810,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4863,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4913,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5063,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5113,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5163,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5213,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5263,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5313,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5363,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5413,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5463,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5513,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5563,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5613,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5663,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5713,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5763,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5813,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5863,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5913,7 +5910,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5963,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6013,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6063,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6113,7 +6110,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6163,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6213,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6263,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6313,7 +6310,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6363,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6413,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6463,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6513,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6763,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6813,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6863,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6913,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6963,7 +6960,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -7013,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7063,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7113,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7163,7 +7160,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7213,7 +7210,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7242,7 +7239,7 @@
         <v>3.77</v>
       </c>
       <c r="P101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7292,7 +7289,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7342,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7392,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7442,7 +7439,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7471,7 +7468,7 @@
         <v>3.75</v>
       </c>
       <c r="P106" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7521,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7571,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7621,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7671,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7700,7 +7697,7 @@
         <v>3.68</v>
       </c>
       <c r="P111" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7750,7 +7747,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7800,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7850,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7900,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7950,7 +7947,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8000,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8050,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8100,7 +8097,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8150,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8200,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8250,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8300,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8350,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8400,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8450,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8500,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8550,7 +8547,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8600,7 +8597,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8650,7 +8647,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8700,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8750,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8800,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8850,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8900,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8950,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9000,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9050,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9100,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9150,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9200,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9250,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9300,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9350,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9400,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9429,7 +9426,7 @@
         <v>2.84</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9479,7 +9476,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9529,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9579,7 +9576,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9629,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9679,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9729,7 +9726,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9779,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9829,7 +9826,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9879,7 +9876,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9929,7 +9926,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9979,7 +9976,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10029,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10079,7 +10076,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10129,7 +10126,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10158,7 +10155,7 @@
         <v>2.78</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10208,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10258,7 +10255,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10308,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10358,7 +10355,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10408,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10458,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="P167" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10508,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10558,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10608,7 +10605,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10658,7 +10655,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10708,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10758,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10808,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10858,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10908,7 +10905,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10958,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11008,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11058,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11108,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11158,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11208,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11258,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11308,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11358,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11408,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11458,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11508,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11558,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11608,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11658,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11708,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11758,7 +11755,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11808,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11858,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -12008,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -12058,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12208,7 +12205,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12258,7 +12255,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12737,7 +12734,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12787,7 +12784,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12837,7 +12834,7 @@
         <v>0</v>
       </c>
       <c r="P215" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12887,7 +12884,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12916,7 +12913,7 @@
         <v>3.29</v>
       </c>
       <c r="P217" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12945,7 +12942,7 @@
         <v>3.29</v>
       </c>
       <c r="P218" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12995,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13045,7 +13042,7 @@
         <v>0</v>
       </c>
       <c r="P220" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13095,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="P221" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13145,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13195,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="P223" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13245,7 +13242,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13295,7 +13292,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13345,7 +13342,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13395,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="P227" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13445,7 +13442,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13495,7 +13492,7 @@
         <v>0</v>
       </c>
       <c r="P229" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13545,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13595,7 +13592,7 @@
         <v>0</v>
       </c>
       <c r="P231" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13645,7 +13642,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13695,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="P233" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13745,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13795,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13845,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13895,7 +13892,7 @@
         <v>0</v>
       </c>
       <c r="P237" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13945,7 +13942,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13995,7 +13992,7 @@
         <v>0</v>
       </c>
       <c r="P239" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -14045,7 +14042,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14095,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14145,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14195,7 +14192,7 @@
         <v>0</v>
       </c>
       <c r="P243" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14245,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14295,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14345,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14374,7 +14371,7 @@
         <v>4.22</v>
       </c>
       <c r="P247" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14424,7 +14421,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14474,7 +14471,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14524,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14574,7 +14571,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14624,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14674,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14724,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14774,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14803,7 +14800,7 @@
         <v>4.35</v>
       </c>
       <c r="P256" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14832,7 +14829,7 @@
         <v>4.24</v>
       </c>
       <c r="P257" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14882,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14932,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14982,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -15032,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15082,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15132,7 +15129,7 @@
         <v>0</v>
       </c>
       <c r="P263" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15182,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15232,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="P265" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15282,7 +15279,7 @@
         <v>0</v>
       </c>
       <c r="P266" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15332,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="P267" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15382,7 +15379,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15432,7 +15429,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15482,7 +15479,7 @@
         <v>0</v>
       </c>
       <c r="P270" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15532,7 +15529,7 @@
         <v>0</v>
       </c>
       <c r="P271" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15582,7 +15579,7 @@
         <v>0</v>
       </c>
       <c r="P272" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15632,7 +15629,7 @@
         <v>0</v>
       </c>
       <c r="P273" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15682,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15732,7 +15729,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15782,7 +15779,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15832,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15882,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15932,7 +15929,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15982,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16332,7 +16329,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16382,7 +16379,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16432,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16482,7 +16479,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16532,7 +16529,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16582,7 +16579,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16632,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16682,7 +16679,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16732,7 +16729,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16782,7 +16779,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16832,7 +16829,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16882,7 +16879,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17532,7 +17529,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17582,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17632,7 +17629,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17682,7 +17679,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17732,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17782,7 +17779,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17832,7 +17829,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17882,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17932,7 +17929,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17982,7 +17979,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18032,7 +18029,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18082,7 +18079,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18132,7 +18129,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18182,7 +18179,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18232,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18282,7 +18279,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18332,7 +18329,7 @@
         <v>0</v>
       </c>
       <c r="P327" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18382,7 +18379,7 @@
         <v>0</v>
       </c>
       <c r="P328" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18432,7 +18429,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18482,7 +18479,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18532,7 +18529,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18582,7 +18579,7 @@
         <v>0</v>
       </c>
       <c r="P332" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18632,7 +18629,7 @@
         <v>0</v>
       </c>
       <c r="P333" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18682,7 +18679,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18732,7 +18729,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18782,7 +18779,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18832,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="P337" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18882,7 +18879,7 @@
         <v>0</v>
       </c>
       <c r="P338" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18932,7 +18929,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18982,7 +18979,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19032,7 +19029,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19082,7 +19079,7 @@
         <v>0</v>
       </c>
       <c r="P342" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19132,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="P343" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19182,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="P344" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19232,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19282,7 +19279,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19332,7 +19329,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19382,7 +19379,7 @@
         <v>0</v>
       </c>
       <c r="P348" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19432,7 +19429,7 @@
         <v>0</v>
       </c>
       <c r="P349" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19482,7 +19479,7 @@
         <v>0</v>
       </c>
       <c r="P350" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19782,7 +19779,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19832,7 +19829,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19882,7 +19879,7 @@
         <v>0</v>
       </c>
       <c r="P358" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19932,7 +19929,7 @@
         <v>0</v>
       </c>
       <c r="P359" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19982,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="P360" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20032,7 +20029,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20082,7 +20079,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20132,7 +20129,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20182,7 +20179,7 @@
         <v>0</v>
       </c>
       <c r="P364" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20232,7 +20229,7 @@
         <v>0</v>
       </c>
       <c r="P365" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20282,7 +20279,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20332,7 +20329,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20382,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20432,7 +20429,7 @@
         <v>0</v>
       </c>
       <c r="P369" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20482,7 +20479,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20532,7 +20529,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20582,7 +20579,7 @@
         <v>0</v>
       </c>
       <c r="P372" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20632,7 +20629,7 @@
         <v>0</v>
       </c>
       <c r="P373" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20682,7 +20679,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20732,7 +20729,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20782,7 +20779,7 @@
         <v>0</v>
       </c>
       <c r="P376" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20832,7 +20829,7 @@
         <v>0</v>
       </c>
       <c r="P377" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21032,7 +21029,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21082,7 +21079,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21132,7 +21129,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21282,7 +21279,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21332,7 +21329,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21382,7 +21379,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21432,7 +21429,7 @@
         <v>0</v>
       </c>
       <c r="P389" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21461,7 +21458,7 @@
         <v>3.81</v>
       </c>
       <c r="P390" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21490,7 +21487,7 @@
         <v>3.89</v>
       </c>
       <c r="P391" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21540,7 +21537,7 @@
         <v>0</v>
       </c>
       <c r="P392" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21590,7 +21587,7 @@
         <v>0</v>
       </c>
       <c r="P393" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21640,7 +21637,7 @@
         <v>0</v>
       </c>
       <c r="P394" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21690,7 +21687,7 @@
         <v>0</v>
       </c>
       <c r="P395" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21740,7 +21737,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21790,7 +21787,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21840,7 +21837,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21890,7 +21887,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21990,7 +21987,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22140,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22190,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22240,7 +22237,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22340,7 +22337,7 @@
         <v>0</v>
       </c>
       <c r="P408" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22390,7 +22387,7 @@
         <v>0</v>
       </c>
       <c r="P409" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22419,7 +22416,7 @@
         <v>4.29</v>
       </c>
       <c r="P410" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22448,7 +22445,7 @@
         <v>4.23</v>
       </c>
       <c r="P411" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22498,7 +22495,7 @@
         <v>0</v>
       </c>
       <c r="P412" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22548,7 +22545,7 @@
         <v>0</v>
       </c>
       <c r="P413" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22598,7 +22595,7 @@
         <v>0</v>
       </c>
       <c r="P414" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22648,7 +22645,7 @@
         <v>0</v>
       </c>
       <c r="P415" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22698,7 +22695,7 @@
         <v>0</v>
       </c>
       <c r="P416" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22748,7 +22745,7 @@
         <v>0</v>
       </c>
       <c r="P417" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22798,7 +22795,7 @@
         <v>0</v>
       </c>
       <c r="P418" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22848,7 +22845,7 @@
         <v>0</v>
       </c>
       <c r="P419" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22898,7 +22895,7 @@
         <v>0</v>
       </c>
       <c r="P420" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22948,7 +22945,7 @@
         <v>0</v>
       </c>
       <c r="P421" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22998,7 +22995,7 @@
         <v>0</v>
       </c>
       <c r="P422" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23048,7 +23045,7 @@
         <v>0</v>
       </c>
       <c r="P423" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23098,7 +23095,7 @@
         <v>0</v>
       </c>
       <c r="P424" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23148,7 +23145,7 @@
         <v>0</v>
       </c>
       <c r="P425" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23198,7 +23195,7 @@
         <v>0</v>
       </c>
       <c r="P426" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23248,7 +23245,7 @@
         <v>0</v>
       </c>
       <c r="P427" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23298,7 +23295,7 @@
         <v>0</v>
       </c>
       <c r="P428" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23348,7 +23345,7 @@
         <v>0</v>
       </c>
       <c r="P429" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23377,7 +23374,7 @@
         <v>4.44</v>
       </c>
       <c r="P430" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23406,7 +23403,7 @@
         <v>4.47</v>
       </c>
       <c r="P431" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23435,7 +23432,7 @@
         <v>4.42</v>
       </c>
       <c r="P432" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23464,7 +23461,7 @@
         <v>4.22</v>
       </c>
       <c r="P433" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23493,7 +23490,7 @@
         <v>4.14</v>
       </c>
       <c r="P434" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23543,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="P435" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23593,7 +23590,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23643,7 +23640,7 @@
         <v>0</v>
       </c>
       <c r="P437" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23693,7 +23690,7 @@
         <v>0</v>
       </c>
       <c r="P438" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23743,7 +23740,7 @@
         <v>0</v>
       </c>
       <c r="P439" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23793,7 +23790,7 @@
         <v>0</v>
       </c>
       <c r="P440" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23843,7 +23840,7 @@
         <v>0</v>
       </c>
       <c r="P441" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23893,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="P442" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23943,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23993,7 +23990,7 @@
         <v>0</v>
       </c>
       <c r="P444" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24043,7 +24040,7 @@
         <v>0</v>
       </c>
       <c r="P445" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24093,7 +24090,7 @@
         <v>0</v>
       </c>
       <c r="P446" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24143,7 +24140,7 @@
         <v>0</v>
       </c>
       <c r="P447" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24193,7 +24190,7 @@
         <v>0</v>
       </c>
       <c r="P448" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24243,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="P449" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24293,7 +24290,7 @@
         <v>0</v>
       </c>
       <c r="P450" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24343,7 +24340,7 @@
         <v>0</v>
       </c>
       <c r="P451" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24393,7 +24390,7 @@
         <v>0</v>
       </c>
       <c r="P452" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24443,7 +24440,7 @@
         <v>0</v>
       </c>
       <c r="P453" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24493,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="P454" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24543,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="P455" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24593,7 +24590,7 @@
         <v>0</v>
       </c>
       <c r="P456" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24643,7 +24640,7 @@
         <v>0</v>
       </c>
       <c r="P457" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24693,7 +24690,7 @@
         <v>0</v>
       </c>
       <c r="P458" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24743,7 +24740,7 @@
         <v>0</v>
       </c>
       <c r="P459" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24793,7 +24790,7 @@
         <v>0</v>
       </c>
       <c r="P460" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24843,7 +24840,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24893,7 +24890,7 @@
         <v>0</v>
       </c>
       <c r="P462" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24943,7 +24940,7 @@
         <v>0</v>
       </c>
       <c r="P463" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24993,7 +24990,7 @@
         <v>0</v>
       </c>
       <c r="P464" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25043,7 +25040,7 @@
         <v>0</v>
       </c>
       <c r="P465" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25093,7 +25090,7 @@
         <v>0</v>
       </c>
       <c r="P466" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25143,7 +25140,7 @@
         <v>0</v>
       </c>
       <c r="P467" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25193,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="P468" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25243,7 +25240,7 @@
         <v>0</v>
       </c>
       <c r="P469" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25293,7 +25290,7 @@
         <v>0</v>
       </c>
       <c r="P470" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25343,7 +25340,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25393,7 +25390,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25443,7 +25440,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25493,7 +25490,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25543,7 +25540,7 @@
         <v>0</v>
       </c>
       <c r="P475" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25593,7 +25590,7 @@
         <v>0</v>
       </c>
       <c r="P476" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25643,7 +25640,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25693,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25743,7 +25740,7 @@
         <v>0</v>
       </c>
       <c r="P479" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25793,7 +25790,7 @@
         <v>0</v>
       </c>
       <c r="P480" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25843,7 +25840,7 @@
         <v>0</v>
       </c>
       <c r="P481" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25893,7 +25890,7 @@
         <v>0</v>
       </c>
       <c r="P482" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25943,7 +25940,7 @@
         <v>0</v>
       </c>
       <c r="P483" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25993,7 +25990,7 @@
         <v>0</v>
       </c>
       <c r="P484" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26043,7 +26040,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26093,7 +26090,7 @@
         <v>0</v>
       </c>
       <c r="P486" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26143,7 +26140,7 @@
         <v>0</v>
       </c>
       <c r="P487" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26193,7 +26190,7 @@
         <v>0</v>
       </c>
       <c r="P488" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26243,7 +26240,7 @@
         <v>0</v>
       </c>
       <c r="P489" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26293,7 +26290,7 @@
         <v>0</v>
       </c>
       <c r="P490" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26343,7 +26340,7 @@
         <v>0</v>
       </c>
       <c r="P491" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26393,7 +26390,7 @@
         <v>0</v>
       </c>
       <c r="P492" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26443,7 +26440,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26493,7 +26490,7 @@
         <v>0</v>
       </c>
       <c r="P494" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26543,7 +26540,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26593,7 +26590,7 @@
         <v>0</v>
       </c>
       <c r="P496" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26643,7 +26640,7 @@
         <v>0</v>
       </c>
       <c r="P497" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26693,7 +26690,7 @@
         <v>0</v>
       </c>
       <c r="P498" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26743,7 +26740,7 @@
         <v>0</v>
       </c>
       <c r="P499" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26793,7 +26790,7 @@
         <v>0</v>
       </c>
       <c r="P500" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26843,7 +26840,7 @@
         <v>0</v>
       </c>
       <c r="P501" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26893,7 +26890,7 @@
         <v>0</v>
       </c>
       <c r="P502" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26943,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="P503" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26993,7 +26990,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27043,7 +27040,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27093,7 +27090,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27143,7 +27140,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27193,7 +27190,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27243,7 +27240,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27293,7 +27290,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27343,7 +27340,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27443,7 +27440,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27493,7 +27490,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27543,7 +27540,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27593,7 +27590,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27643,7 +27640,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27693,7 +27690,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27743,7 +27740,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27793,7 +27790,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27843,7 +27840,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27893,7 +27890,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27943,7 +27940,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27993,7 +27990,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28043,7 +28040,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28093,7 +28090,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28143,7 +28140,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -29593,7 +29590,7 @@
         <v>0</v>
       </c>
       <c r="P556" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29643,7 +29640,7 @@
         <v>0</v>
       </c>
       <c r="P557" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29693,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="P558" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29743,7 +29740,7 @@
         <v>0</v>
       </c>
       <c r="P559" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29793,7 +29790,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29843,7 +29840,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29893,7 +29890,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29943,7 +29940,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29993,7 +29990,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30043,7 +30040,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30093,7 +30090,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30143,7 +30140,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30172,7 +30169,7 @@
         <v>3.63</v>
       </c>
       <c r="P568" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30222,7 +30219,7 @@
         <v>0</v>
       </c>
       <c r="P569" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30251,7 +30248,7 @@
         <v>3.7</v>
       </c>
       <c r="P570" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30280,7 +30277,7 @@
         <v>3.7</v>
       </c>
       <c r="P571" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30330,7 +30327,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30380,7 +30377,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30430,7 +30427,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30480,7 +30477,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30530,7 +30527,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30580,7 +30577,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30630,7 +30627,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30680,7 +30677,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30730,7 +30727,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30780,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30830,7 +30827,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30880,7 +30877,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30930,7 +30927,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30980,7 +30977,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31030,7 +31027,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31080,7 +31077,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31180,7 +31177,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31230,7 +31227,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31280,7 +31277,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31330,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31380,7 +31377,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31430,7 +31427,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31480,7 +31477,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31530,7 +31527,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31580,7 +31577,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31630,7 +31627,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31680,7 +31677,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31730,7 +31727,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31880,7 +31877,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31930,7 +31927,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31980,7 +31977,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32030,7 +32027,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32080,7 +32077,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32130,7 +32127,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32159,7 +32156,7 @@
         <v>3.4</v>
       </c>
       <c r="P609" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32209,7 +32206,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32259,7 +32256,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32309,7 +32306,7 @@
         <v>0</v>
       </c>
       <c r="P612" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32359,7 +32356,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32409,7 +32406,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32459,7 +32456,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32509,7 +32506,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32559,7 +32556,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32609,7 +32606,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32659,7 +32656,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32709,7 +32706,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32759,7 +32756,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32809,7 +32806,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32859,7 +32856,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32909,7 +32906,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32959,7 +32956,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33009,7 +33006,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33059,7 +33056,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33109,7 +33106,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33159,7 +33156,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33209,7 +33206,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33259,7 +33256,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33309,7 +33306,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33359,7 +33356,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33409,7 +33406,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33459,7 +33456,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33509,7 +33506,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33709,7 +33706,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33759,7 +33756,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33809,7 +33806,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34009,7 +34006,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34059,7 +34056,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34109,7 +34106,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34159,7 +34156,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34209,7 +34206,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34259,7 +34256,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34309,7 +34306,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34359,7 +34356,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34409,7 +34406,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34438,7 +34435,7 @@
         <v>3.69</v>
       </c>
       <c r="P655" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34488,7 +34485,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34538,7 +34535,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34588,7 +34585,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34638,7 +34635,7 @@
         <v>0</v>
       </c>
       <c r="P659" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34688,7 +34685,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34738,7 +34735,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34788,7 +34785,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34838,7 +34835,7 @@
         <v>0</v>
       </c>
       <c r="P663" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34888,7 +34885,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34938,7 +34935,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34988,7 +34985,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35017,7 +35014,7 @@
         <v>3.69</v>
       </c>
       <c r="P667" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35046,7 +35043,7 @@
         <v>3.61</v>
       </c>
       <c r="P668" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35096,7 +35093,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35146,7 +35143,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35196,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35246,7 +35243,7 @@
         <v>0</v>
       </c>
       <c r="P672" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35296,7 +35293,7 @@
         <v>0</v>
       </c>
       <c r="P673" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35346,7 +35343,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35396,7 +35393,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35446,7 +35443,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35496,7 +35493,7 @@
         <v>0</v>
       </c>
       <c r="P677" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35546,7 +35543,7 @@
         <v>0</v>
       </c>
       <c r="P678" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35596,7 +35593,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35646,7 +35643,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35696,7 +35693,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35746,7 +35743,7 @@
         <v>0</v>
       </c>
       <c r="P682" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35796,7 +35793,7 @@
         <v>0</v>
       </c>
       <c r="P683" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35846,7 +35843,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35896,7 +35893,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35946,7 +35943,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35996,7 +35993,7 @@
         <v>0</v>
       </c>
       <c r="P687" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36046,7 +36043,7 @@
         <v>0</v>
       </c>
       <c r="P688" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36096,7 +36093,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36146,7 +36143,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36196,7 +36193,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36246,7 +36243,7 @@
         <v>0</v>
       </c>
       <c r="P692" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36296,7 +36293,7 @@
         <v>0</v>
       </c>
       <c r="P693" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36346,7 +36343,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36396,7 +36393,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36446,7 +36443,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36496,7 +36493,7 @@
         <v>0</v>
       </c>
       <c r="P697" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36546,7 +36543,7 @@
         <v>0</v>
       </c>
       <c r="P698" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36596,7 +36593,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36646,7 +36643,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36696,7 +36693,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36746,7 +36743,7 @@
         <v>0</v>
       </c>
       <c r="P702" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36796,7 +36793,7 @@
         <v>0</v>
       </c>
       <c r="P703" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36846,7 +36843,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36896,7 +36893,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36946,7 +36943,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36996,7 +36993,7 @@
         <v>0</v>
       </c>
       <c r="P707" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37046,7 +37043,7 @@
         <v>0</v>
       </c>
       <c r="P708" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37096,7 +37093,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37146,7 +37143,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37196,7 +37193,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37246,7 +37243,7 @@
         <v>0</v>
       </c>
       <c r="P712" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37296,7 +37293,7 @@
         <v>0</v>
       </c>
       <c r="P713" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37346,7 +37343,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37396,7 +37393,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37446,7 +37443,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37496,7 +37493,7 @@
         <v>0</v>
       </c>
       <c r="P717" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37546,7 +37543,7 @@
         <v>0</v>
       </c>
       <c r="P718" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37596,7 +37593,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37646,7 +37643,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37696,7 +37693,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37746,7 +37743,7 @@
         <v>0</v>
       </c>
       <c r="P722" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37796,7 +37793,7 @@
         <v>0</v>
       </c>
       <c r="P723" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38096,7 +38093,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38146,7 +38143,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38196,7 +38193,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38246,7 +38243,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38296,7 +38293,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38346,7 +38343,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38396,7 +38393,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38446,7 +38443,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38596,7 +38593,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38646,7 +38643,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38696,7 +38693,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38746,7 +38743,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38925,7 +38922,7 @@
         <v>0</v>
       </c>
       <c r="P746" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39025,7 +39022,7 @@
         <v>0</v>
       </c>
       <c r="P748" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39075,7 +39072,7 @@
         <v>0</v>
       </c>
       <c r="P749" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39125,7 +39122,7 @@
         <v>0</v>
       </c>
       <c r="P750" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39175,7 +39172,7 @@
         <v>0</v>
       </c>
       <c r="P751" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39225,7 +39222,7 @@
         <v>0</v>
       </c>
       <c r="P752" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39275,7 +39272,7 @@
         <v>0</v>
       </c>
       <c r="P753" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39325,7 +39322,7 @@
         <v>0</v>
       </c>
       <c r="P754" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39375,7 +39372,7 @@
         <v>0</v>
       </c>
       <c r="P755" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39425,7 +39422,7 @@
         <v>0</v>
       </c>
       <c r="P756" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39475,7 +39472,7 @@
         <v>0</v>
       </c>
       <c r="P757" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39525,7 +39522,7 @@
         <v>0</v>
       </c>
       <c r="P758" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39575,7 +39572,7 @@
         <v>0</v>
       </c>
       <c r="P759" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39625,7 +39622,7 @@
         <v>0</v>
       </c>
       <c r="P760" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39675,7 +39672,7 @@
         <v>0</v>
       </c>
       <c r="P761" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39725,7 +39722,7 @@
         <v>0</v>
       </c>
       <c r="P762" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39775,7 +39772,7 @@
         <v>0</v>
       </c>
       <c r="P763" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39825,7 +39822,7 @@
         <v>0</v>
       </c>
       <c r="P764" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -39925,7 +39922,7 @@
         <v>0</v>
       </c>
       <c r="P766" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39975,7 +39972,7 @@
         <v>0</v>
       </c>
       <c r="P767" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40025,7 +40022,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40075,7 +40072,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40125,7 +40122,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40175,7 +40172,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40225,7 +40222,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40275,7 +40272,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40325,7 +40322,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40375,7 +40372,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40425,7 +40422,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40475,7 +40472,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40525,7 +40522,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40575,7 +40572,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40625,7 +40622,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40675,7 +40672,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40725,7 +40722,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40775,7 +40772,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40825,7 +40822,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -40875,7 +40872,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -40925,7 +40922,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -40975,7 +40972,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41025,7 +41022,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41075,7 +41072,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41125,7 +41122,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41175,7 +41172,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41225,7 +41222,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41275,7 +41272,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41325,7 +41322,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41375,7 +41372,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41425,7 +41422,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41475,7 +41472,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41525,7 +41522,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41575,7 +41572,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41625,7 +41622,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41675,7 +41672,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41725,7 +41722,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41775,7 +41772,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41825,7 +41822,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41875,7 +41872,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -41925,7 +41922,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -41975,7 +41972,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42025,7 +42022,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42075,7 +42072,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42125,7 +42122,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42175,7 +42172,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42225,7 +42222,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42275,7 +42272,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42325,7 +42322,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42375,7 +42372,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42425,7 +42422,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42475,7 +42472,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42525,7 +42522,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42575,7 +42572,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42625,7 +42622,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42675,7 +42672,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42725,7 +42722,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42775,7 +42772,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42825,7 +42822,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -42875,7 +42872,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -42925,7 +42922,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -42975,7 +42972,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43025,7 +43022,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43075,7 +43072,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43125,7 +43122,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43175,7 +43172,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43225,7 +43222,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43275,7 +43272,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43325,7 +43322,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43375,7 +43372,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43425,7 +43422,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43475,7 +43472,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43525,7 +43522,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43575,7 +43572,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43589,10 +43586,10 @@
         <v>-0.4565025608378592</v>
       </c>
       <c r="D840" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E840">
-        <v>-0.181480555537135</v>
+        <v>-0.2214845565009029</v>
       </c>
       <c r="F840">
         <v>1</v>
@@ -43601,10 +43598,10 @@
         <v>0.00585650256083786</v>
       </c>
       <c r="H840">
-        <v>0.005581480555537135</v>
+        <v>0.005641484556500902</v>
       </c>
       <c r="I840">
-        <v>0.2750220053007242</v>
+        <v>0.2350180043369563</v>
       </c>
       <c r="J840">
         <v>0.6250500120471009</v>
@@ -43616,16 +43613,16 @@
         <v>2.7</v>
       </c>
       <c r="M840">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="N840">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O840">
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43675,7 +43672,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43689,10 +43686,10 @@
         <v>-0.4706749540699158</v>
       </c>
       <c r="D842" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E842">
-        <v>-0.1944181263885771</v>
+        <v>-0.2346466405124565</v>
       </c>
       <c r="F842">
         <v>1</v>
@@ -43701,10 +43698,10 @@
         <v>0.005870674954069916</v>
       </c>
       <c r="H842">
-        <v>0.005594418126388577</v>
+        <v>0.005654646640512457</v>
       </c>
       <c r="I842">
-        <v>0.2762568276813386</v>
+        <v>0.2360283135574592</v>
       </c>
       <c r="J842">
         <v>0.6278564265484983</v>
@@ -43716,16 +43713,16 @@
         <v>2.7</v>
       </c>
       <c r="M842">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="N842">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O842">
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43775,51 +43772,51 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="844" spans="1:16">
       <c r="A844" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B844" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C844">
-        <v>-0.4801344054283416</v>
+        <v>-0.008765444084921192</v>
       </c>
       <c r="D844" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E844">
-        <v>-0.243431754744341</v>
+        <v>-0.3577180367494308</v>
       </c>
       <c r="F844">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G844">
-        <v>0.005880134405428341</v>
+        <v>0.006308765444084921</v>
       </c>
       <c r="H844">
-        <v>0.005663431754744341</v>
+        <v>0.005997718036749431</v>
       </c>
       <c r="I844">
-        <v>0.2367026506840006</v>
+        <v>0.3489525926645096</v>
       </c>
       <c r="J844">
-        <v>0.629729585233335</v>
+        <v>0.6317530888169842</v>
       </c>
       <c r="K844">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="L844">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M844">
-        <v>4.69</v>
+        <v>5.03</v>
       </c>
       <c r="N844">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="O844">
         <v>1</v>
@@ -43836,28 +43833,28 @@
         <v>108</v>
       </c>
       <c r="C845">
-        <v>-0.008765444084921192</v>
+        <v>-0.01826244241108999</v>
       </c>
       <c r="D845" t="s">
         <v>264</v>
       </c>
       <c r="E845">
-        <v>-0.3577180367494308</v>
+        <v>-0.3672720170655568</v>
       </c>
       <c r="F845">
         <v>-1</v>
       </c>
       <c r="G845">
-        <v>0.006308765444084921</v>
+        <v>0.00631826244241109</v>
       </c>
       <c r="H845">
-        <v>0.005997718036749431</v>
+        <v>0.006007272017065557</v>
       </c>
       <c r="I845">
-        <v>0.3489525926645096</v>
+        <v>0.3490095746544668</v>
       </c>
       <c r="J845">
-        <v>0.6317530888169842</v>
+        <v>0.633652488482218</v>
       </c>
       <c r="K845">
         <v>5</v>
@@ -43883,43 +43880,43 @@
         <v>0</v>
       </c>
       <c r="B846" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C846">
-        <v>-0.01826244241108999</v>
+        <v>0.1126630239428299</v>
       </c>
       <c r="D846" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E846">
-        <v>-0.3672720170655568</v>
+        <v>0.3688350017702726</v>
       </c>
       <c r="F846">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G846">
-        <v>0.00631826244241109</v>
+        <v>0.005287336976057171</v>
       </c>
       <c r="H846">
-        <v>0.006007272017065557</v>
+        <v>0.005031164998229727</v>
       </c>
       <c r="I846">
-        <v>0.3490095746544668</v>
+        <v>0.2561719778274427</v>
       </c>
       <c r="J846">
-        <v>0.633652488482218</v>
+        <v>0.5123439556548852</v>
       </c>
       <c r="K846">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="L846">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="M846">
-        <v>5.03</v>
+        <v>4.55</v>
       </c>
       <c r="N846">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="O846">
         <v>1</v>
@@ -43936,28 +43933,28 @@
         <v>111</v>
       </c>
       <c r="C847">
-        <v>0.1126630239428299</v>
+        <v>0.3334339927459959</v>
       </c>
       <c r="D847" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E847">
-        <v>0.3688350017702726</v>
+        <v>0.59147284523665</v>
       </c>
       <c r="F847">
         <v>1</v>
       </c>
       <c r="G847">
-        <v>0.005287336976057171</v>
+        <v>0.005066566007254004</v>
       </c>
       <c r="H847">
-        <v>0.005031164998229727</v>
+        <v>0.00466852715476335</v>
       </c>
       <c r="I847">
-        <v>0.2561719778274427</v>
+        <v>0.2580388524906541</v>
       </c>
       <c r="J847">
-        <v>0.5123439556548852</v>
+        <v>0.4686269321295058</v>
       </c>
       <c r="K847">
         <v>5.05</v>
@@ -43966,13 +43963,13 @@
         <v>2.7</v>
       </c>
       <c r="M847">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="N847">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O847">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P847" t="s">
         <v>608</v>
@@ -43986,28 +43983,28 @@
         <v>111</v>
       </c>
       <c r="C848">
-        <v>0.3334339927459959</v>
+        <v>0.3469472497139483</v>
       </c>
       <c r="D848" t="s">
         <v>269</v>
       </c>
       <c r="E848">
-        <v>0.59147284523665</v>
+        <v>0.6031129774763713</v>
       </c>
       <c r="F848">
         <v>1</v>
       </c>
       <c r="G848">
-        <v>0.005066566007254004</v>
+        <v>0.005053052750286052</v>
       </c>
       <c r="H848">
-        <v>0.00466852715476335</v>
+        <v>0.004656887022523629</v>
       </c>
       <c r="I848">
-        <v>0.2580388524906541</v>
+        <v>0.256165727762423</v>
       </c>
       <c r="J848">
-        <v>0.4686269321295058</v>
+        <v>0.4659510396606044</v>
       </c>
       <c r="K848">
         <v>5.05</v>
@@ -44022,7 +44019,7 @@
         <v>2.63</v>
       </c>
       <c r="O848">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P848" t="s">
         <v>609</v>
@@ -44036,28 +44033,28 @@
         <v>111</v>
       </c>
       <c r="C849">
-        <v>0.3469472497139483</v>
+        <v>0.351648458141776</v>
       </c>
       <c r="D849" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E849">
-        <v>0.561751019062795</v>
+        <v>0.6071625332508366</v>
       </c>
       <c r="F849">
         <v>1</v>
       </c>
       <c r="G849">
-        <v>0.005053052750286052</v>
+        <v>0.005048351541858224</v>
       </c>
       <c r="H849">
-        <v>0.004578248980937205</v>
+        <v>0.004652837466749164</v>
       </c>
       <c r="I849">
-        <v>0.2148037693488467</v>
+        <v>0.2555140751090605</v>
       </c>
       <c r="J849">
-        <v>0.4659510396606044</v>
+        <v>0.4650201072986582</v>
       </c>
       <c r="K849">
         <v>5.05</v>
@@ -44066,10 +44063,10 @@
         <v>2.7</v>
       </c>
       <c r="M849">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="N849">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="O849">
         <v>0</v>
@@ -44086,28 +44083,28 @@
         <v>111</v>
       </c>
       <c r="C850">
-        <v>0.351648458141776</v>
+        <v>0.3567649219326281</v>
       </c>
       <c r="D850" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E850">
-        <v>0.5657633375427831</v>
+        <v>0.6115697842389962</v>
       </c>
       <c r="F850">
         <v>1</v>
       </c>
       <c r="G850">
-        <v>0.005048351541858224</v>
+        <v>0.005043235078067372</v>
       </c>
       <c r="H850">
-        <v>0.004574236662457217</v>
+        <v>0.004648430215761003</v>
       </c>
       <c r="I850">
-        <v>0.214114879401007</v>
+        <v>0.2548048623063681</v>
       </c>
       <c r="J850">
-        <v>0.4650201072986582</v>
+        <v>0.4640069461519549</v>
       </c>
       <c r="K850">
         <v>5.05</v>
@@ -44116,10 +44113,10 @@
         <v>2.7</v>
       </c>
       <c r="M850">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="N850">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="O850">
         <v>0</v>
@@ -44136,28 +44133,28 @@
         <v>111</v>
       </c>
       <c r="C851">
-        <v>0.3567649219326281</v>
+        <v>0.3589258596081755</v>
       </c>
       <c r="D851" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E851">
-        <v>0.5701300620850742</v>
+        <v>0.6134311859991213</v>
       </c>
       <c r="F851">
         <v>1</v>
       </c>
       <c r="G851">
-        <v>0.005043235078067372</v>
+        <v>0.005041074140391824</v>
       </c>
       <c r="H851">
-        <v>0.004569869937914925</v>
+        <v>0.004646568814000878</v>
       </c>
       <c r="I851">
-        <v>0.2133651401524461</v>
+        <v>0.2545053263909458</v>
       </c>
       <c r="J851">
-        <v>0.4640069461519549</v>
+        <v>0.4635790377013514</v>
       </c>
       <c r="K851">
         <v>5.05</v>
@@ -44166,10 +44163,10 @@
         <v>2.7</v>
       </c>
       <c r="M851">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="N851">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="O851">
         <v>0</v>
@@ -44186,28 +44183,28 @@
         <v>111</v>
       </c>
       <c r="C852">
-        <v>0.3589258596081755</v>
+        <v>0.3582480273744801</v>
       </c>
       <c r="D852" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E852">
-        <v>0.5719743475071752</v>
+        <v>0.6128473107087102</v>
       </c>
       <c r="F852">
         <v>1</v>
       </c>
       <c r="G852">
-        <v>0.005041074140391824</v>
+        <v>0.005041751972625521</v>
       </c>
       <c r="H852">
-        <v>0.004568025652492824</v>
+        <v>0.004647152689291289</v>
       </c>
       <c r="I852">
-        <v>0.2130484878989998</v>
+        <v>0.2545992833342301</v>
       </c>
       <c r="J852">
-        <v>0.4635790377013514</v>
+        <v>0.4637132619060436</v>
       </c>
       <c r="K852">
         <v>5.05</v>
@@ -44216,66 +44213,16 @@
         <v>2.7</v>
       </c>
       <c r="M852">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="N852">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="O852">
         <v>0</v>
       </c>
       <c r="P852" t="s">
         <v>613</v>
-      </c>
-    </row>
-    <row r="853" spans="1:16">
-      <c r="A853" s="1">
-        <v>0</v>
-      </c>
-      <c r="B853" t="s">
-        <v>111</v>
-      </c>
-      <c r="C853">
-        <v>0.3582480273744801</v>
-      </c>
-      <c r="D853" t="s">
-        <v>270</v>
-      </c>
-      <c r="E853">
-        <v>0.571395841184952</v>
-      </c>
-      <c r="F853">
-        <v>1</v>
-      </c>
-      <c r="G853">
-        <v>0.005041751972625521</v>
-      </c>
-      <c r="H853">
-        <v>0.004568604158815048</v>
-      </c>
-      <c r="I853">
-        <v>0.2131478138104719</v>
-      </c>
-      <c r="J853">
-        <v>0.4637132619060436</v>
-      </c>
-      <c r="K853">
-        <v>5.05</v>
-      </c>
-      <c r="L853">
-        <v>2.7</v>
-      </c>
-      <c r="M853">
-        <v>4.31</v>
-      </c>
-      <c r="N853">
-        <v>2.57</v>
-      </c>
-      <c r="O853">
-        <v>0</v>
-      </c>
-      <c r="P853" t="s">
-        <v>614</v>
       </c>
     </row>
   </sheetData>
